--- a/context_DB/DRC_context_db.xlsx
+++ b/context_DB/DRC_context_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK59"/>
+  <dimension ref="A1:BL61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -686,60 +686,65 @@
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
+          <t>fatalities</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>event_count_evt3</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>ADM1_PCODE_evt3</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>event_type</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>sub_event_type</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>actor1</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>assoc_actor_1</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>actor2</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>assoc_actor_2</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>event_date</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
           <t>admin2</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>fatalities</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>event_count_evt3</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>event_type</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>sub_event_type</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>actor1</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>assoc_actor_1</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>actor2</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>assoc_actor_2</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>event_date</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>ratio IDP/ToTN - HPC2025</t>
         </is>
@@ -762,7 +767,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -847,58 +852,63 @@
           <t>Ituri</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="AZ2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>Ituri</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>Strategic developments ---- Protests ---- Protests ---- Protests ---- Protests ---- Violence against civilians</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>Agreement ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Attack</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>Unidentified Armed Group (Democratic Republic of Congo) ---- Protesters (Democratic Republic of Congo) ---- Protesters (Democratic Republic of Congo) ---- Protesters (Democratic Republic of Congo) ---- Protesters (Democratic Republic of Congo) ---- Military Forces of the Democratic Republic of Congo (2019-)</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>Mayi Mayi Militia (Chini Ya Tuna) ---- REC: National Student Representation; Students (Democratic Republic of Congo) ---- Students (Democratic Republic of Congo) ---- Students (Democratic Republic of Congo) ---- Teachers (Democratic Republic of Congo)</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Government of the Democratic Republic of Congo (2019-) ---- Civilians (Democratic Republic of Congo)</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>Labor Group (Democratic Republic of Congo); Students (Democratic Republic of Congo)</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>On 29 January 2024, over 100 youth members from different armed group including Chini ya Tuna, from five communities affected by armed group attacks in the Djugu territory, joined the 'Aru Act' agreement (signed in early June) at the Official Primary School in the city of Bunia (Baboa-Bakoe, Irumu, Ituri). The agreement is part of the peace process and the Disarmament, Demobilization, Community Reintegration, and Stabilization Program (DDRCS). The ceremony involved youths from the Mambisa, Ndo-Okebo, Nyali, Alur, and Hema communities. ---- On 13 February 2024, the national student representation (REC) of Ituri mobilized about a hundred students protesters from various universities in Bunia (Baboa-Bakoe, Bunia, Ituri) to stage a march to express support for the FARDC who are fighting the M23/RDF in Nord-Kivu. They also showed solidarity with the victims of atrocities committed by armed groups in eastern DRC. ---- On 9 July 2024, students at the Bunia Institute of Medical Technology (ISTM Bunia) staged a protest in Bunia (Baboa-Bakoe, Bunia, Ituri) to condemn the murder of their colleague killed on 8 July by unidentified armed group. The Police Commander intervened to calm the situation. The victim's body was transported from the crime scene to the morgue at Balidja Decore under the supervision of the Congolese National Police. ---- On 4 October 2024, mobile phone users (Telecom subscribers), including students, protested in Bunia city (Baboa-Bakoe, Bunia, Ituri) to denounce the poor internet connection provided by the operator(s). ---- On 6 November 2024, Public primary school teachers in the Ituri 1 educational province, including Bunia, coded to territorial capital Bunia (Baboa-Bakoe, Bunia, Ituri), Irumu, Djugu, and Mambasa, protested to demand the formalization of new units and a base salary of 500 US dollars before resuming classes. ---- On 14 March 2025, one FARDC soldier killed four people in Bunia (Bunia, Ituri), including 3 agents from ISTM-Bunia (University) and one student, according to University reports.</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>2024-01-29 ---- 2024-02-13 ---- 2024-07-09 ---- 2024-10-04 ---- 2024-11-06 ---- 2025-03-14</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
         <is>
           <t>Bunia</t>
         </is>
       </c>
-      <c r="BA2" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>Violence against civilians ---- Protests ---- Protests ---- Protests ---- Protests ---- Strategic developments</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>Attack ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Agreement</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>Military Forces of the Democratic Republic of Congo (2019-) ---- Protesters (Democratic Republic of Congo) ---- Protesters (Democratic Republic of Congo) ---- Protesters (Democratic Republic of Congo) ---- Protesters (Democratic Republic of Congo) ---- Mayi Mayi Militia</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>Teachers (Democratic Republic of Congo) ---- Students (Democratic Republic of Congo) ---- Students (Democratic Republic of Congo) ---- REC: National Student Representation; Students (Democratic Republic of Congo)</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>Civilians (Democratic Republic of Congo) ---- Government of the Democratic Republic of Congo (2019-)</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>Labor Group (Democratic Republic of Congo); Students (Democratic Republic of Congo)</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>On 14 March 2025, one FARDC soldier killed four people in Bunia (Bunia, Ituri), including 3 agents from ISTM-Bunia (University) and one student, according to University reports. ---- On 6 November 2024, Public primary school teachers in the Ituri 1 educational province, including Bunia, coded to territorial capital Bunia (Baboa-Bakoe, Bunia, Ituri), Irumu, Djugu, and Mambasa, protested to demand the formalization of new units and a base salary of 500 US dollars before resuming classes. ---- On 4 October 2024, mobile phone users (Telecom subscribers), including students, protested in Bunia city (Baboa-Bakoe, Bunia, Ituri) to denounce the poor internet connection provided by the operator(s). ---- On 9 July 2024, students at the Bunia Institute of Medical Technology (ISTM Bunia) staged a protest in Bunia (Baboa-Bakoe, Bunia, Ituri) to condemn the murder of their colleague killed on 8 July by unidentified armed group. The Police Commander intervened to calm the situation. The victim's body was transported from the crime scene to the morgue at Balidja Decore under the supervision of the Congolese National Police. ---- On 13 February 2024, the national student representation (REC) of Ituri mobilized about a hundred students protesters from various universities in Bunia (Baboa-Bakoe, Bunia, Ituri) to stage a march to express support for the FARDC who are fighting the M23/RDF in Nord-Kivu. They also showed solidarity with the victims of atrocities committed by armed groups in eastern DRC. ---- On 29 January 2024, over 100 youths members of self-defense group from five communities victims armed groups attacks in Djugu territory agreed to join the peace process and the Disarmament, Demobilization, Community Reintegration, and Stabilization Program (DDRCS) during a ceremony held at the Official Primary School in the city of Bunia (Baboa-Bakoe, Irumu, Ituri). These youths hailed from Mambisa, Ndo-Okebo, Nyali, Alur, and Hema communities.</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>14 March 2025 ---- 06 November 2024 ---- 04 October 2024 ---- 09 July 2024 ---- 13 February 2024 ---- 29 January 2024</t>
-        </is>
-      </c>
-      <c r="BK2" t="n">
+      <c r="BL2" t="n">
         <v>0.07367498697484962</v>
       </c>
     </row>
@@ -919,7 +929,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CD5402ZS03;CD5402ZS06;CD5405ZS09;CD5405ZS12;CD5407ZS06;CD6104ZS01;CD6107ZS05;CD6201ZS02;CD6202ZS01;CD6205ZS01;CD6207ZS01;CD6207ZS02;CD6208ZS04;CD6212ZS03</t>
+          <t>CD5402ZS03;CD5402ZS06;CD5405ZS12;CD5407ZS06;CD6104ZS01;CD6107ZS05;CD6201ZS02;CD6202ZS01;CD6205ZS01;CD6207ZS01;CD6207ZS02;CD6208ZS04;CD6212ZS03</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -1011,7 +1021,8 @@
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr"/>
       <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="n">
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="n">
         <v>0.02801511386458794</v>
       </c>
     </row>
@@ -1032,7 +1043,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1124,7 +1135,8 @@
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr"/>
       <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="n">
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="n">
         <v>0.1022658947621584</v>
       </c>
     </row>
@@ -1145,7 +1157,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CD5402ZS03;CD5402ZS06;CD5405ZS09;CD5405ZS12;CD5407ZS06;CD6104ZS01;CD6107ZS05;CD6201ZS02;CD6202ZS01;CD6205ZS01;CD6207ZS01;CD6207ZS02;CD6208ZS04;CD6212ZS03</t>
+          <t>CD5402ZS03;CD5402ZS06;CD5405ZS12;CD5407ZS06;CD6104ZS01;CD6107ZS05;CD6201ZS02;CD6202ZS01;CD6205ZS01;CD6207ZS01;CD6207ZS02;CD6208ZS04;CD6212ZS03</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1203,7 +1215,7 @@
         <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1230,13 +1242,13 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ5" t="n">
         <v>2</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1248,42 +1260,42 @@
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2025-03-14 ---- 2024-05-17</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t xml:space="preserve">May 2024: A primary school was attacked overnight by CODECO fighters who opened fire towards the building. Two children were shot and three women injured._x000D_
+          <t xml:space="preserve">March 2025: A student was shot and injured an en educational faclity by a FARDC soldier who was reportedly drunk. ---- May 2024: A primary school was attacked overnight by CODECO fighters who opened fire towards the building. Two children were shot and three women injured._x000D_
 </t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Education Building </t>
+          <t xml:space="preserve">Education Building  ---- Education Building </t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>NSA</t>
+          <t>Other ---- NSA</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>Coalition of Congolese Democrats (Armed Wing)</t>
+          <t>Forces Arm√©es de la R√©publique D√©mocratique du Congo ---- Coalition of Congolese Democrats (Armed Wing)</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>Firearms</t>
+          <t>Firearms ---- Firearms</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>Primary School</t>
+          <t>University ---- Primary School</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr"/>
@@ -1300,7 +1312,8 @@
       <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="inlineStr"/>
       <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="n">
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="n">
         <v>0.5497430553911005</v>
       </c>
     </row>
@@ -1321,7 +1334,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1413,7 +1426,8 @@
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr"/>
       <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="n">
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="n">
         <v>0.2742741748601318</v>
       </c>
     </row>
@@ -1434,7 +1448,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1526,7 +1540,8 @@
       <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr"/>
       <c r="BJ7" t="inlineStr"/>
-      <c r="BK7" t="n">
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="n">
         <v>0.3236186448469247</v>
       </c>
     </row>
@@ -1547,7 +1562,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1639,7 +1654,8 @@
       <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="inlineStr"/>
       <c r="BJ8" t="inlineStr"/>
-      <c r="BK8" t="n">
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="n">
         <v>0.1126484851181207</v>
       </c>
     </row>
@@ -1660,7 +1676,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1740,19 +1756,64 @@
       <c r="AV9" t="inlineStr"/>
       <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="inlineStr"/>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Ituri</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>Ituri</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>Violence against civilians</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>FPAC: Ituri Self-Defense Popular Front (Zaire)</t>
+        </is>
+      </c>
       <c r="BF9" t="inlineStr"/>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
-      <c r="BI9" t="inlineStr"/>
-      <c r="BJ9" t="inlineStr"/>
-      <c r="BK9" t="n">
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Civilians (Democratic Republic of Congo)</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>Labor Group (Democratic Republic of Congo); Students (Democratic Republic of Congo)</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>On 29 June 2025, overnight, Zaire attacked civilians in Masumboko (Walendu-Tatsi, Djugu, Ituri). They killed two people, a student and a tax collector. Residents fled.</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>Djugu</t>
+        </is>
+      </c>
+      <c r="BL9" t="n">
         <v>0.06783589743589744</v>
       </c>
     </row>
@@ -1773,7 +1834,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1853,59 +1914,20 @@
       <c r="AV10" t="inlineStr"/>
       <c r="AW10" t="inlineStr"/>
       <c r="AX10" t="inlineStr"/>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Ituri</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>Djugu</t>
-        </is>
-      </c>
-      <c r="BA10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>Strategic developments ---- Violence against civilians</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>Other ---- Attack</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>Civilians (Democratic Republic of Congo) ---- CODECO: Cooperative for Development of Congo</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>Teachers (Democratic Republic of Congo)</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>Civilians (Democratic Republic of Congo)</t>
-        </is>
-      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
       <c r="BH10" t="inlineStr"/>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>Other: On 17 February 2025, schools in Fataki, Djaiba and Lilo, coded to Djaiba (Djugu, Ituri) extended its closure due to the security situation, as CODECO attacks continue. At least 5 thousand chldren are affected by this closure. ---- On 17 May 2024, overnight, CODECO attacked a primary school in Petsi (Walendu-Djatsi, Djugu, Ituri). They shot dead two children and severely injured three women, two of whom later died. 4 fatalities.</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>17 February 2025 ---- 17 May 2024</t>
-        </is>
-      </c>
-      <c r="BK10" t="n">
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="n">
         <v>0.02440654471645338</v>
       </c>
     </row>
@@ -1926,7 +1948,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -2018,7 +2040,8 @@
       <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr"/>
       <c r="BJ11" t="inlineStr"/>
-      <c r="BK11" t="n">
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="n">
         <v>0.05858913471562609</v>
       </c>
     </row>
@@ -2039,7 +2062,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2131,7 +2154,8 @@
       <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="inlineStr"/>
       <c r="BJ12" t="inlineStr"/>
-      <c r="BK12" t="n">
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="n">
         <v>0.0347291603318709</v>
       </c>
     </row>
@@ -2152,7 +2176,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2244,7 +2268,8 @@
       <c r="BH13" t="inlineStr"/>
       <c r="BI13" t="inlineStr"/>
       <c r="BJ13" t="inlineStr"/>
-      <c r="BK13" t="n">
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="n">
         <v>0.4389537043917663</v>
       </c>
     </row>
@@ -2260,12 +2285,12 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD6205ZS01</t>
+          <t>CD5405ZS09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CD5402ZS03;CD5402ZS06;CD5405ZS09;CD5405ZS12;CD5407ZS06;CD6104ZS01;CD6107ZS05;CD6201ZS02;CD6202ZS01;CD6205ZS01;CD6207ZS01;CD6207ZS02;CD6208ZS04;CD6212ZS03</t>
+          <t>CD5405ZS09</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -2357,7 +2382,8 @@
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr"/>
       <c r="BJ14" t="inlineStr"/>
-      <c r="BK14" t="n">
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="n">
         <v>0.05156550398242241</v>
       </c>
     </row>
@@ -2378,7 +2404,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -2532,7 +2558,8 @@
       <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr"/>
       <c r="BJ15" t="inlineStr"/>
-      <c r="BK15" t="n">
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="n">
         <v>0.1807199211045365</v>
       </c>
     </row>
@@ -2553,7 +2580,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CD5402ZS03;CD5402ZS06;CD5405ZS09;CD5405ZS12;CD5407ZS06;CD6104ZS01;CD6107ZS05;CD6201ZS02;CD6202ZS01;CD6205ZS01;CD6207ZS01;CD6207ZS02;CD6208ZS04;CD6212ZS03</t>
+          <t>CD5402ZS03;CD5402ZS06;CD5405ZS12;CD5407ZS06;CD6104ZS01;CD6107ZS05;CD6201ZS02;CD6202ZS01;CD6205ZS01;CD6207ZS01;CD6207ZS02;CD6208ZS04;CD6212ZS03</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -2638,16 +2665,16 @@
           <t>Ituri</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>Djugu</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
         <v>1</v>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>Ituri</t>
+        </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
@@ -2678,10 +2705,15 @@
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>09 August 2024</t>
-        </is>
-      </c>
-      <c r="BK16" t="n">
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr">
+        <is>
+          <t>Djugu</t>
+        </is>
+      </c>
+      <c r="BL16" t="n">
         <v>0.1722110401445394</v>
       </c>
     </row>
@@ -2702,7 +2734,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -2794,7 +2826,8 @@
       <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr"/>
       <c r="BJ17" t="inlineStr"/>
-      <c r="BK17" t="n">
+      <c r="BK17" t="inlineStr"/>
+      <c r="BL17" t="n">
         <v>0.05185803037275656</v>
       </c>
     </row>
@@ -2815,7 +2848,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -2907,7 +2940,8 @@
       <c r="BH18" t="inlineStr"/>
       <c r="BI18" t="inlineStr"/>
       <c r="BJ18" t="inlineStr"/>
-      <c r="BK18" t="n">
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="n">
         <v>0.05066744051073709</v>
       </c>
     </row>
@@ -2928,7 +2962,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -3013,16 +3047,16 @@
           <t>Ituri</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>Mahagi</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
         <v>1</v>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>Ituri</t>
+        </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
@@ -3053,10 +3087,15 @@
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>29 January 2024</t>
-        </is>
-      </c>
-      <c r="BK19" t="n">
+          <t>2024-01-29</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>Mahagi</t>
+        </is>
+      </c>
+      <c r="BL19" t="n">
         <v>0.2915579462887881</v>
       </c>
     </row>
@@ -3072,12 +3111,12 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CD5403ZS04</t>
+          <t>CD5407ZS03</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5407ZS03</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -3169,7 +3208,8 @@
       <c r="BH20" t="inlineStr"/>
       <c r="BI20" t="inlineStr"/>
       <c r="BJ20" t="inlineStr"/>
-      <c r="BK20" t="n">
+      <c r="BK20" t="inlineStr"/>
+      <c r="BL20" t="n">
         <v>0.03308499559400785</v>
       </c>
     </row>
@@ -3190,7 +3230,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -3282,7 +3322,8 @@
       <c r="BH21" t="inlineStr"/>
       <c r="BI21" t="inlineStr"/>
       <c r="BJ21" t="inlineStr"/>
-      <c r="BK21" t="n">
+      <c r="BK21" t="inlineStr"/>
+      <c r="BL21" t="n">
         <v>0.06717964285242915</v>
       </c>
     </row>
@@ -3303,7 +3344,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -3395,7 +3436,8 @@
       <c r="BH22" t="inlineStr"/>
       <c r="BI22" t="inlineStr"/>
       <c r="BJ22" t="inlineStr"/>
-      <c r="BK22" t="n">
+      <c r="BK22" t="inlineStr"/>
+      <c r="BL22" t="n">
         <v>0.3650409633254523</v>
       </c>
     </row>
@@ -3416,7 +3458,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>CD5402ZS03;CD5402ZS06;CD5405ZS09;CD5405ZS12;CD5407ZS06;CD6104ZS01;CD6107ZS05;CD6201ZS02;CD6202ZS01;CD6205ZS01;CD6207ZS01;CD6207ZS02;CD6208ZS04;CD6212ZS03</t>
+          <t>CD5402ZS03;CD5402ZS06;CD5405ZS12;CD5407ZS06;CD6104ZS01;CD6107ZS05;CD6201ZS02;CD6202ZS01;CD6205ZS01;CD6207ZS01;CD6207ZS02;CD6208ZS04;CD6212ZS03</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -3508,7 +3550,8 @@
       <c r="BH23" t="inlineStr"/>
       <c r="BI23" t="inlineStr"/>
       <c r="BJ23" t="inlineStr"/>
-      <c r="BK23" t="n">
+      <c r="BK23" t="inlineStr"/>
+      <c r="BL23" t="n">
         <v>0.145754774772322</v>
       </c>
     </row>
@@ -3529,7 +3572,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -3621,7 +3664,8 @@
       <c r="BH24" t="inlineStr"/>
       <c r="BI24" t="inlineStr"/>
       <c r="BJ24" t="inlineStr"/>
-      <c r="BK24" t="n">
+      <c r="BK24" t="inlineStr"/>
+      <c r="BL24" t="n">
         <v>0.01073398685921085</v>
       </c>
     </row>
@@ -3642,7 +3686,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -3734,7 +3778,8 @@
       <c r="BH25" t="inlineStr"/>
       <c r="BI25" t="inlineStr"/>
       <c r="BJ25" t="inlineStr"/>
-      <c r="BK25" t="n">
+      <c r="BK25" t="inlineStr"/>
+      <c r="BL25" t="n">
         <v>0.02359388839681134</v>
       </c>
     </row>
@@ -3755,7 +3800,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -3840,65 +3885,70 @@
           <t>Nord-Kivu</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
+      <c r="AZ26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>Nord-Kivu</t>
+        </is>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>Violence against civilians ---- Strategic developments ---- Strategic developments</t>
+        </is>
+      </c>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>Attack ---- Other ---- Other</t>
+        </is>
+      </c>
+      <c r="BE26" t="inlineStr">
+        <is>
+          <t>EPLC: Awakening of Patriots for the Liberation of Congo (Wazalendo) ---- Civilians (Democratic Republic of Congo) ---- Government of the Democratic Republic of Congo (2019-)</t>
+        </is>
+      </c>
+      <c r="BF26" t="inlineStr">
+        <is>
+          <t>Refugees/IDPs (Democratic Republic of Congo)</t>
+        </is>
+      </c>
+      <c r="BG26" t="inlineStr">
+        <is>
+          <t>Civilians (Democratic Republic of Congo) ---- Civilians (Democratic Republic of Congo)</t>
+        </is>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>Students (Democratic Republic of Congo) ---- Caritas; Teachers (Democratic Republic of Congo)</t>
+        </is>
+      </c>
+      <c r="BI26" t="inlineStr">
+        <is>
+          <t>On 4 November 2024, an EPLC Wazalendo shot dead a school student in Goma (Goma, Nord-Kivu), after the militant requested 500 FC from the student who could not pay. Youth then protested (coded separately). ---- Other: Around 24 January 2025 (as reported), electricity, water and internet cuts, as well as closure of schools, and supply shortages started in Goma (Goma, Nord-Kivu), following intense clashes between M23 and FARDC and allies. Also 10 radio stations stopped their services. ---- Other: Around 18 April 2025, the government of DRC completed four months without paying the salaries of school teachers in Rutshuru, Masisi, Goma, and Nyiragongo, coded to Goma (Goma, Nord-Kivu). The most affected are the teachers paid by CARITAS - Goma. The reason for this delay is the closure of banks due to M23's occupation.</t>
+        </is>
+      </c>
+      <c r="BJ26" t="inlineStr">
+        <is>
+          <t>2024-11-04 ---- 2025-01-24 ---- 2025-04-18</t>
+        </is>
+      </c>
+      <c r="BK26" t="inlineStr">
         <is>
           <t>Goma</t>
         </is>
       </c>
-      <c r="BA26" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>3</v>
-      </c>
-      <c r="BC26" t="inlineStr">
-        <is>
-          <t>Strategic developments ---- Strategic developments ---- Violence against civilians</t>
-        </is>
-      </c>
-      <c r="BD26" t="inlineStr">
-        <is>
-          <t>Other ---- Other ---- Attack</t>
-        </is>
-      </c>
-      <c r="BE26" t="inlineStr">
-        <is>
-          <t>Government of the Democratic Republic of Congo (2019-) ---- Civilians (Democratic Republic of Congo) ---- EPLC: Awakening of Patriots for the Liberation of Congo (Wazalendo)</t>
-        </is>
-      </c>
-      <c r="BF26" t="inlineStr">
-        <is>
-          <t>Refugees/IDPs (Democratic Republic of Congo)</t>
-        </is>
-      </c>
-      <c r="BG26" t="inlineStr">
-        <is>
-          <t>Civilians (Democratic Republic of Congo) ---- Civilians (Democratic Republic of Congo)</t>
-        </is>
-      </c>
-      <c r="BH26" t="inlineStr">
-        <is>
-          <t>Caritas; Teachers (Democratic Republic of Congo) ---- Students (Democratic Republic of Congo)</t>
-        </is>
-      </c>
-      <c r="BI26" t="inlineStr">
-        <is>
-          <t>Other: Around 18 April 2025, the government of DRC completed four months without paying the salaries of school teachers in Rutshuru, Masisi, Goma, and Nyiragongo, coded to Goma (Goma, Nord-Kivu). The most affected are the teachers paid by CARITAS - Goma. The reason for this delay is the closure of banks due to M23's occupation. ---- Other: Around 24 January 2025 (as reported), electricity, water and internet cuts, as well as closure of schools, and supply shortages started in Goma (Goma, Nord-Kivu), following intense clashes between M23 and FARDC and allies. Also 10 radio stations stopped their services. ---- On 4 November 2024, an EPLC Wazalendo shot dead a school student in Goma (Goma, Nord-Kivu), after the militant requested 500 FC from the student who could not pay. Youth then protested (coded separately).</t>
-        </is>
-      </c>
-      <c r="BJ26" t="inlineStr">
-        <is>
-          <t>18 April 2025 ---- 24 January 2025 ---- 04 November 2024</t>
-        </is>
-      </c>
-      <c r="BK26" t="n">
+      <c r="BL26" t="n">
         <v>0.05442158369256293</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CD6104ZS01</t>
+          <t>CD6101ZS02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -3907,37 +3957,37 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CD6207ZS02</t>
+          <t>CD6101ZS01</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CD5402ZS03;CD5402ZS06;CD5405ZS09;CD5405ZS12;CD5407ZS06;CD6104ZS01;CD6107ZS05;CD6201ZS02;CD6202ZS01;CD6205ZS01;CD6207ZS01;CD6207ZS02;CD6208ZS04;CD6212ZS03</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>60.6</v>
+        <v>32.2</v>
       </c>
       <c r="I27" t="n">
-        <v>37.7</v>
+        <v>50</v>
       </c>
       <c r="J27" t="n">
-        <v>1.7</v>
+        <v>16.6</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="L27" t="n">
-        <v>39.4</v>
+        <v>67.8</v>
       </c>
       <c r="M27" t="n">
-        <v>67.73999999999999</v>
+        <v>175.58</v>
       </c>
       <c r="N27" t="n">
-        <v>8.85</v>
+        <v>9.82</v>
       </c>
       <c r="O27" t="n">
-        <v>3.39</v>
+        <v>1.25</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -3949,10 +3999,10 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>4.949999999999999</v>
+        <v>16.38</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>10.54</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -3961,7 +4011,7 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>10.67</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -3997,57 +4047,70 @@
           <t>Nord-Kivu</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>Walikale</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>1</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>Nord-Kivu</t>
+        </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>Strategic developments ---- Strategic developments</t>
+          <t>Riots ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Protests ---- Violence against civilians ---- Strategic developments ---- Strategic developments</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>Disrupted weapons use ---- Headquarters or base established</t>
+          <t>Mob violence ---- Shelling/artillery/missile attack ---- Shelling/artillery/missile attack ---- Peaceful protest ---- Abduction/forced disappearance ---- Other ---- Other</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
-          <t>Military Forces of the Democratic Republic of Congo (2019-) ---- Unidentified Armed Group (Democratic Republic of Congo)</t>
-        </is>
-      </c>
-      <c r="BF27" t="inlineStr"/>
+          <t>Rioters (Democratic Republic of Congo) ---- M23: March 23 Movement ---- M23: March 23 Movement ---- Protesters (Democratic Republic of Congo) ---- Unidentified Armed Group (Democratic Republic of Congo) ---- Civilians (Democratic Republic of Congo) ---- Civilians (Democratic Republic of Congo)</t>
+        </is>
+      </c>
+      <c r="BF27" t="inlineStr">
+        <is>
+          <t>Students (Democratic Republic of Congo); Vigilante Group (Democratic Republic of Congo) ---- Military Forces of Rwanda (1994-) ---- Students (Democratic Republic of Congo) ---- Refugees/IDPs (Democratic Republic of Congo) ---- Refugees/IDPs (Democratic Republic of Congo)</t>
+        </is>
+      </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>M23: March 23 Movement</t>
-        </is>
-      </c>
-      <c r="BH27" t="inlineStr"/>
+          <t>Civilians (Democratic Republic of Congo) ---- Civilians (Democratic Republic of Congo) ---- Civilians (Democratic Republic of Congo)</t>
+        </is>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>Labor Group (Democratic Republic of Congo)</t>
+        </is>
+      </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>Defusal: Around 19 April 2025, FARDC discovered an unexploded device, suspected to have been left by M23, near a secondary school in Kibua (Walikale, Nord-Kivu) and defused it. ---- Around 2 May 2024 (as reported), unidentified armed group established a base within a school premise, in the village of Nsengu (Walikale, Nord-Kivu).</t>
+          <t>On 19 January 2024, residents and the local population set fire to a truck and lynched the driver in the Ndosho neighborhood, west of the city of Goma - Ndosho (Karisimbi, Goma, Nord-Kivu), after the truck was involved in a traffic accident killing one female student and injuring two others. ---- On 2 February 2024, M23 fired shells at the Nengapeta school complex school in the Mugunga neighborhood, southeast of Goma, in the Karisimbi commune Goma - Mugunga (Goma, Nord-Kivu). At least 3 people have been severely injured and houses damaged in the aftermath of the explosion. ---- On 7 February 2024, M23/RDF fired a bomb targeting civilians in the Kisoko market, not far from Cinquantenaire School, in the Goma - Mugunga neighborhood (Karisimbi, Goma, Nord-Kivu). No fatalities, but some material damage has been recorded. The bomb created panic among the local population. ---- On 4 November 2024, students from Institut Mubi protested in Goma - Ndosho (Goma, Nord-Kivu), after one of their peers was killed by a Wazalendo the same day (coded separately). ---- On 3 February 2025, unidentified armed men held families captive near Balindu primary school in Goma - Ndosho (Goma, Nord-Kivu). Casualties unknown. ---- Displacement: Around 24 February 2025 (as reported), around 5 thousand people who were expelled from Katindo camp found shelter in schools in Karisimbi, coded to Goma - Majengo (Goma, Nord-Kivu). ---- Displacement: Around 24 February 2025 (as reported), around 5 thousand people who were expelled from Katindo camp found shelter in schools in Karisimbi, coded to Goma - Majengo (Goma, Nord-Kivu).</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>19 April 2025 ---- 02 May 2024</t>
-        </is>
-      </c>
-      <c r="BK27" t="n">
-        <v>0.0234815278647464</v>
+          <t>2024-01-19 ---- 2024-02-02 ---- 2024-02-07 ---- 2024-11-04 ---- 2025-02-03 ---- 2025-02-24 ---- 2025-02-24</t>
+        </is>
+      </c>
+      <c r="BK27" t="inlineStr">
+        <is>
+          <t>Goma</t>
+        </is>
+      </c>
+      <c r="BL27" t="n">
+        <v>0.05442158369256293</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CD6104ZS04</t>
+          <t>CD6104ZS01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -4056,37 +4119,37 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CD5402ZS04</t>
+          <t>CD6207ZS02</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS03;CD5402ZS06;CD5405ZS12;CD5407ZS06;CD6104ZS01;CD6107ZS05;CD6201ZS02;CD6202ZS01;CD6205ZS01;CD6207ZS01;CD6207ZS02;CD6208ZS04;CD6212ZS03</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>75.7</v>
+        <v>60.6</v>
       </c>
       <c r="I28" t="n">
-        <v>20.8</v>
+        <v>37.7</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>24.3</v>
+        <v>39.4</v>
       </c>
       <c r="M28" t="n">
-        <v>61.31</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="N28" t="n">
-        <v>1.83</v>
+        <v>8.85</v>
       </c>
       <c r="O28" t="n">
-        <v>1.21</v>
+        <v>3.39</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -4098,47 +4161,110 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3.63</v>
+        <v>4.949999999999999</v>
       </c>
       <c r="T28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>7.19</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
       </c>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="inlineStr"/>
-      <c r="AC28" t="inlineStr"/>
-      <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="inlineStr"/>
-      <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="inlineStr"/>
-      <c r="AH28" t="inlineStr"/>
-      <c r="AI28" t="inlineStr"/>
-      <c r="AJ28" t="inlineStr"/>
-      <c r="AK28" t="inlineStr"/>
-      <c r="AL28" t="inlineStr"/>
-      <c r="AM28" t="inlineStr"/>
-      <c r="AN28" t="inlineStr"/>
-      <c r="AO28" t="inlineStr"/>
-      <c r="AP28" t="inlineStr"/>
-      <c r="AQ28" t="inlineStr"/>
-      <c r="AR28" t="inlineStr"/>
-      <c r="AS28" t="inlineStr"/>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AU28" t="inlineStr"/>
-      <c r="AV28" t="inlineStr"/>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>2025-04-19</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">April 2025: In the courtyard of an education facility, an unexploded device suspected to have been left by M23 was discovered and defused by FARDC. _x000D_
+</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building </t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr">
+        <is>
+          <t>March 23 Movement</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>UXO</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>Secondary School</t>
+        </is>
+      </c>
       <c r="AW28" t="inlineStr"/>
       <c r="AX28" t="inlineStr"/>
       <c r="AY28" t="inlineStr"/>
@@ -4153,14 +4279,15 @@
       <c r="BH28" t="inlineStr"/>
       <c r="BI28" t="inlineStr"/>
       <c r="BJ28" t="inlineStr"/>
-      <c r="BK28" t="n">
-        <v>0.009424269264836138</v>
+      <c r="BK28" t="inlineStr"/>
+      <c r="BL28" t="n">
+        <v>0.0234815278647464</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CD6107ZS02</t>
+          <t>CD6104ZS04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -4169,37 +4296,37 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CD5407ZS04</t>
+          <t>CD5402ZS04</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>58.4</v>
+        <v>75.7</v>
       </c>
       <c r="I29" t="n">
-        <v>30</v>
+        <v>20.8</v>
       </c>
       <c r="J29" t="n">
-        <v>11.6</v>
+        <v>0.5</v>
       </c>
       <c r="K29" t="n">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="L29" t="n">
-        <v>41.6</v>
+        <v>24.3</v>
       </c>
       <c r="M29" t="n">
-        <v>122.4</v>
+        <v>61.31</v>
       </c>
       <c r="N29" t="n">
-        <v>26.83</v>
+        <v>1.83</v>
       </c>
       <c r="O29" t="n">
-        <v>0.76</v>
+        <v>1.21</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -4211,69 +4338,180 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W29" t="n">
-        <v>3.79</v>
+        <v>7.19</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
       </c>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="inlineStr"/>
-      <c r="AF29" t="inlineStr"/>
-      <c r="AG29" t="inlineStr"/>
-      <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="inlineStr"/>
-      <c r="AJ29" t="inlineStr"/>
-      <c r="AK29" t="inlineStr"/>
-      <c r="AL29" t="inlineStr"/>
-      <c r="AM29" t="inlineStr"/>
-      <c r="AN29" t="inlineStr"/>
-      <c r="AO29" t="inlineStr"/>
-      <c r="AP29" t="inlineStr"/>
-      <c r="AQ29" t="inlineStr"/>
-      <c r="AR29" t="inlineStr"/>
-      <c r="AS29" t="inlineStr"/>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AU29" t="inlineStr"/>
-      <c r="AV29" t="inlineStr"/>
+      <c r="Y29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>2025-05-18 ---- 2025-04-26</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>May 2025: An educator was killed with a hammer, and phone stolen, by unidentified perpetrators, when travelling to withdraw his salary. ---- April 2025: An education facility was set fire to and destroyed by Ma√Ø Ma√Ø Kifuafua during a wider attack. Books and metal roofing sheets were also stolen.</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unspecified Location ---- Education Building </t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>No Information ---- NSA</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr">
+        <is>
+          <t>No Information ---- Mai Mai militia</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>Other Weapon ---- Arson</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>Not Applicable ---- School: No Further Details</t>
+        </is>
+      </c>
       <c r="AW29" t="inlineStr"/>
       <c r="AX29" t="inlineStr"/>
-      <c r="AY29" t="inlineStr"/>
-      <c r="AZ29" t="inlineStr"/>
-      <c r="BA29" t="inlineStr"/>
-      <c r="BB29" t="inlineStr"/>
-      <c r="BC29" t="inlineStr"/>
-      <c r="BD29" t="inlineStr"/>
-      <c r="BE29" t="inlineStr"/>
-      <c r="BF29" t="inlineStr"/>
-      <c r="BG29" t="inlineStr"/>
-      <c r="BH29" t="inlineStr"/>
-      <c r="BI29" t="inlineStr"/>
-      <c r="BJ29" t="inlineStr"/>
-      <c r="BK29" t="n">
-        <v>0.09494038197741901</v>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Nord-Kivu</t>
+        </is>
+      </c>
+      <c r="AZ29" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>Nord-Kivu</t>
+        </is>
+      </c>
+      <c r="BC29" t="inlineStr">
+        <is>
+          <t>Strategic developments ---- Battles ---- Strategic developments ---- Strategic developments ---- Protests</t>
+        </is>
+      </c>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>Headquarters or base established ---- Armed clash ---- Disrupted weapons use ---- Looting/property destruction ---- Protest with intervention</t>
+        </is>
+      </c>
+      <c r="BE29" t="inlineStr">
+        <is>
+          <t>Unidentified Armed Group (Democratic Republic of Congo) ---- Unidentified Armed Group (Democratic Republic of Congo) ---- Military Forces of the Democratic Republic of Congo (2019-) ---- Mayi Mayi Militia (Kifuafua) ---- Protesters (Democratic Republic of Congo)</t>
+        </is>
+      </c>
+      <c r="BF29" t="inlineStr">
+        <is>
+          <t>Students (Democratic Republic of Congo)</t>
+        </is>
+      </c>
+      <c r="BG29" t="inlineStr">
+        <is>
+          <t>Unidentified Armed Group (Democratic Republic of Congo) ---- M23: March 23 Movement ---- Civilians (Democratic Republic of Congo) ---- Police Forces of the Democratic Republic of Congo (2019-)</t>
+        </is>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>Military Forces of the Democratic Republic of Congo (2019-) Military Police</t>
+        </is>
+      </c>
+      <c r="BI29" t="inlineStr">
+        <is>
+          <t>Around 2 May 2024 (as reported), unidentified armed group established a base within a school premise, in the village of Nsengu (Walikale, Nord-Kivu). ---- On 17 March 2025, two unspecified armed groups clashed against each other near Mukaka (Walikale, Nord-Kivu). Sexual violence incidents and attacks on hospitals and schools took place. Dozens of people were killed. ---- Defusal: Around 19 April 2025, FARDC discovered an unexploded device, suspected to have been left by M23, near a secondary school in Kibua (Walikale, Nord-Kivu) and defused it. ---- Looting: On 26 April 2025, Mayi Mayi Kifuafua looted cattle, set fire to houses and destroyed the primary school in Bagira village, near Waloa Loanda (Walikale, Nord-Kivu). ---- On 18 June 2025, police supported by military police used tear gas to disperse a peaceful protest staged by higher education students in Walikale (Walikale, Nord-Kivu). The protesters were asking for academic activities at ISP, ISDR and ISTM to resume. Classes have been suspended since 26 May as personnel is on strike due to unpaid wages.</t>
+        </is>
+      </c>
+      <c r="BJ29" t="inlineStr">
+        <is>
+          <t>2024-05-02 ---- 2025-03-17 ---- 2025-04-19 ---- 2025-04-26 ---- 2025-06-18</t>
+        </is>
+      </c>
+      <c r="BK29" t="inlineStr">
+        <is>
+          <t>Walikale</t>
+        </is>
+      </c>
+      <c r="BL29" t="n">
+        <v>0.009424269264836138</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CD6107ZS05</t>
+          <t>CD6107ZS02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -4282,37 +4520,37 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CD5402ZS06</t>
+          <t>CD5407ZS04</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>CD5402ZS03;CD5402ZS06;CD5405ZS09;CD5405ZS12;CD5407ZS06;CD6104ZS01;CD6107ZS05;CD6201ZS02;CD6202ZS01;CD6205ZS01;CD6207ZS01;CD6207ZS02;CD6208ZS04;CD6212ZS03</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>64.8</v>
+        <v>58.4</v>
       </c>
       <c r="I30" t="n">
-        <v>31.3</v>
+        <v>30</v>
       </c>
       <c r="J30" t="n">
-        <v>4</v>
+        <v>11.6</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L30" t="n">
-        <v>35.2</v>
+        <v>41.6</v>
       </c>
       <c r="M30" t="n">
-        <v>84.31</v>
+        <v>122.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>26.83</v>
       </c>
       <c r="O30" t="n">
-        <v>2.86</v>
+        <v>0.76</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
@@ -4324,19 +4562,19 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>14.29</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
@@ -4379,14 +4617,15 @@
       <c r="BH30" t="inlineStr"/>
       <c r="BI30" t="inlineStr"/>
       <c r="BJ30" t="inlineStr"/>
-      <c r="BK30" t="n">
-        <v>0.08928872455917555</v>
+      <c r="BK30" t="inlineStr"/>
+      <c r="BL30" t="n">
+        <v>0.09494038197741901</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CD6107ZS06</t>
+          <t>CD6107ZS05</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -4395,61 +4634,61 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CD5405ZS07</t>
+          <t>CD5402ZS06</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS03;CD5402ZS06;CD5405ZS12;CD5407ZS06;CD6104ZS01;CD6107ZS05;CD6201ZS02;CD6202ZS01;CD6205ZS01;CD6207ZS01;CD6207ZS02;CD6208ZS04;CD6212ZS03</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>67.5</v>
+        <v>64.8</v>
       </c>
       <c r="I31" t="n">
-        <v>29.7</v>
+        <v>31.3</v>
       </c>
       <c r="J31" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="K31" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>32.5</v>
+        <v>35.2</v>
       </c>
       <c r="M31" t="n">
-        <v>123.37</v>
+        <v>84.31</v>
       </c>
       <c r="N31" t="n">
-        <v>6.54</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>1.19</v>
+        <v>2.86</v>
       </c>
       <c r="P31" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3.16</v>
+        <v>14.29</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U31" t="n">
-        <v>4.55</v>
+        <v>0.92</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
@@ -4480,60 +4719,21 @@
       <c r="AV31" t="inlineStr"/>
       <c r="AW31" t="inlineStr"/>
       <c r="AX31" t="inlineStr"/>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Nord-Kivu</t>
-        </is>
-      </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>Beni</t>
-        </is>
-      </c>
-      <c r="BA31" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC31" t="inlineStr">
-        <is>
-          <t>Violence against civilians</t>
-        </is>
-      </c>
-      <c r="BD31" t="inlineStr">
-        <is>
-          <t>Attack</t>
-        </is>
-      </c>
-      <c r="BE31" t="inlineStr">
-        <is>
-          <t>ADF: Allied Democratic Forces</t>
-        </is>
-      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr"/>
+      <c r="BA31" t="inlineStr"/>
+      <c r="BB31" t="inlineStr"/>
+      <c r="BC31" t="inlineStr"/>
+      <c r="BD31" t="inlineStr"/>
+      <c r="BE31" t="inlineStr"/>
       <c r="BF31" t="inlineStr"/>
-      <c r="BG31" t="inlineStr">
-        <is>
-          <t>Civilians (Democratic Republic of Congo)</t>
-        </is>
-      </c>
-      <c r="BH31" t="inlineStr">
-        <is>
-          <t>Teachers (Democratic Republic of Congo)</t>
-        </is>
-      </c>
-      <c r="BI31" t="inlineStr">
-        <is>
-          <t>On 4 March 2025, ADF militants killed a teacher from Kasanga Tuha Institute near Mapera, closest location Matiba (Oicha, Beni).</t>
-        </is>
-      </c>
-      <c r="BJ31" t="inlineStr">
-        <is>
-          <t>04 March 2025</t>
-        </is>
-      </c>
-      <c r="BK31" t="n">
-        <v>0.2517680222194586</v>
+      <c r="BG31" t="inlineStr"/>
+      <c r="BH31" t="inlineStr"/>
+      <c r="BI31" t="inlineStr"/>
+      <c r="BJ31" t="inlineStr"/>
+      <c r="BK31" t="inlineStr"/>
+      <c r="BL31" t="n">
+        <v>0.08928872455917555</v>
       </c>
     </row>
     <row r="32">
@@ -4553,7 +4753,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -4607,30 +4807,92 @@
       <c r="X32" t="n">
         <v>0</v>
       </c>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
-      <c r="AB32" t="inlineStr"/>
-      <c r="AC32" t="inlineStr"/>
-      <c r="AD32" t="inlineStr"/>
-      <c r="AE32" t="inlineStr"/>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="inlineStr"/>
-      <c r="AH32" t="inlineStr"/>
-      <c r="AI32" t="inlineStr"/>
-      <c r="AJ32" t="inlineStr"/>
-      <c r="AK32" t="inlineStr"/>
-      <c r="AL32" t="inlineStr"/>
-      <c r="AM32" t="inlineStr"/>
-      <c r="AN32" t="inlineStr"/>
-      <c r="AO32" t="inlineStr"/>
-      <c r="AP32" t="inlineStr"/>
-      <c r="AQ32" t="inlineStr"/>
-      <c r="AR32" t="inlineStr"/>
-      <c r="AS32" t="inlineStr"/>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AU32" t="inlineStr"/>
-      <c r="AV32" t="inlineStr"/>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>March 2025: A teacher was killed by ADF.</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>Unspecified Location</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr">
+        <is>
+          <t>Allied Democratic Forces /National Army for the Liberation of Uganda</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>Firearms</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="AW32" t="inlineStr"/>
       <c r="AX32" t="inlineStr"/>
       <c r="AY32" t="inlineStr">
@@ -4638,61 +4900,70 @@
           <t>Nord-Kivu</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>Bordj Badji Mokhtar</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>3</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>Nord-Kivu</t>
+        </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>Violence against civilians</t>
+          <t>Violence against civilians ---- Violence against civilians ---- Strategic developments ---- Riots ---- Protests ---- Violence against civilians ---- Riots ---- Riots ---- Protests ---- Violence against civilians ---- Protests</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>Abduction/forced disappearance</t>
+          <t>Attack ---- Attack ---- Disrupted weapons use ---- Mob violence ---- Protest with intervention ---- Attack ---- Violent demonstration ---- Violent demonstration ---- Peaceful protest ---- Attack ---- Peaceful protest</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
-          <t>Unidentified Armed Group (Democratic Republic of Congo)</t>
-        </is>
-      </c>
-      <c r="BF32" t="inlineStr"/>
+          <t>ADF: Allied Democratic Forces ---- Unidentified Armed Group (Democratic Republic of Congo) ---- Police Forces of the Democratic Republic of Congo (2019-) ---- Rioters (Democratic Republic of Congo) ---- Protesters (Democratic Republic of Congo) ---- ADF: Allied Democratic Forces ---- Rioters (Democratic Republic of Congo) ---- Rioters (Democratic Republic of Congo) ---- Protesters (Democratic Republic of Congo) ---- Police Forces of the Democratic Republic of Congo (2019-) ---- Protesters (Democratic Republic of Congo)</t>
+        </is>
+      </c>
+      <c r="BF32" t="inlineStr">
+        <is>
+          <t>Students (Democratic Republic of Congo) ---- Students (Democratic Republic of Congo) ---- SYECO: Union of Congolese Teachers; Teachers (Democratic Republic of Congo) ---- Women (Democratic Republic of Congo)</t>
+        </is>
+      </c>
       <c r="BG32" t="inlineStr">
         <is>
-          <t>Civilians (Democratic Republic of Congo)</t>
+          <t>Civilians (Democratic Republic of Congo) ---- Civilians (Democratic Republic of Congo) ---- Unidentified Armed Group (Democratic Republic of Congo) ---- Rioters (Democratic Republic of Congo) ---- Police Forces of the Democratic Republic of Congo (2019-) ---- Civilians (Democratic Republic of Congo) ---- Civilians (Democratic Republic of Congo) ---- Civilians (Democratic Republic of Congo) ---- Civilians (Democratic Republic of Congo)</t>
         </is>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>Teachers (Democratic Republic of Congo)</t>
+          <t>Students (Democratic Republic of Congo) ---- Students (Democratic Republic of Congo) ---- Women (Democratic Republic of Congo) ---- Students (Democratic Republic of Congo) ---- Students (Democratic Republic of Congo) ---- Teachers (Democratic Republic of Congo)</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>On 11 August 2024, an unidentified armed group abducted the prefect of Tuendeleye High School in Mabasele (Beni, Nord-Kivu).</t>
+          <t>On 21 February 2024, suspected ADF beat a civilian in the Bakaiku near Oicha (Beni, Nord-Kivu). There were no fatalities. The victim was the son of a teacher at Afina Institute. The militia looted large amounts of money and fired shots in the air before they fled. ---- On 25 February 2024, an unidentified armed group killed a student during an incursion in the Kabalaka area of the Ngongolio neighborhood in Mulekera (Beni, Nord-Kivu). They also injured another man with gunshots. He had to be hospitalized. They left stealing valuable goods. ---- Defusal: On 27 February 2024, Police officers defused an IED, discovered by the residents in the latrines of a school located north of Oicha, in Tenambo (Beni, Nord-Kivu). The IED was planted by an unidentified armed group. ---- On 6 March 2024, students from the Ahadi Institute attacked and clashed with those from the Mangina Institute in Mangina (Beni, Nord-Kivu) causing damages, including broken windows and perforated metal sheets. Police intervened and arrested 2 students among the rioters. Casualties unknown. ---- On 16 April 2024, protesters, mainly youths in school uniforms, blocked several streets and avenues in the Bungulu and Mulekera communes of Beni city (Beni, Nord-Kivu) to denounce increased attacks carried out by ADF in the neighborhoods of Sayo, Kasanga-Tuha, and the rural commune of Mangina. The police intervened to restore order. ---- On 17 April 2024, ADF militia attacked and killed 1 woman in Kudukudu, 4 kilometers from Mangina (Beni, Beni, Nord-Kivu) while an unknown number were injured and went missing. The militia set fire to 3 motorbikes, houses, and a school. ---- On 22 April 2024, violent demonstrations against insecurity took place in the town of Beni (Beni, Nord-Kivu). Groups of youth who were demonstrating launched rocks at students in at least 23 different schools. At least one student was injured. ---- On 23 April 2024, for the second consecutive day, violent demonstrations against insecurity took place in the town of Beni (Beni, Nord-Kivu). Groups of youth who were demonstrating launched rocks at students in schools. At least one student was injured. ---- On 5 March 2025, teachers and members of several unions, including SYECO, staged a sit-in in front of the town hall of Beni (Nord-Kivu) after the murder of 2 teachers in Ruwenzori and Bungulu. They decided to suspend school activities. ---- Around 8 March 2025 (as reported), an unidentified armed group (likely the police forces based on the location of the incident being 500 meters from the police post) shot and killed a teacher in Boikene (Beni, Beni, Nord-Kivu) for unknown reasons. ---- On 14 July 2025, widows of Congolese soldiers protested at Rond-Point du 30 Juin roundabout in Beni city (Beni, Beni, Nord-Kivu), denouncing government neglect. The protesters blocked (means unspecified) traffic on Boulevard Nyamwisi. The women demanded financial and social support, including adequate survivor pensions, access to healthcare, education for their children, housing assistance, and official recognition of their status.</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr">
         <is>
-          <t>11 August 2024</t>
-        </is>
-      </c>
-      <c r="BK32" t="n">
+          <t>2024-02-21 ---- 2024-02-25 ---- 2024-02-27 ---- 2024-03-06 ---- 2024-04-16 ---- 2024-04-17 ---- 2024-04-22 ---- 2024-04-23 ---- 2025-03-05 ---- 2025-03-08 ---- 2025-07-14</t>
+        </is>
+      </c>
+      <c r="BK32" t="inlineStr">
+        <is>
+          <t>Beni</t>
+        </is>
+      </c>
+      <c r="BL32" t="n">
         <v>0.2517680222194586</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CD6201ZS01</t>
+          <t>CD6107ZS06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -4701,111 +4972,218 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CD6202ZS04</t>
+          <t>CD5405ZS07</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H33" t="n">
         <v>67.5</v>
       </c>
       <c r="I33" t="n">
-        <v>31.8</v>
+        <v>29.7</v>
       </c>
       <c r="J33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K33" t="n">
         <v>0.4</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.3</v>
       </c>
       <c r="L33" t="n">
         <v>32.5</v>
       </c>
       <c r="M33" t="n">
-        <v>71.69999999999999</v>
+        <v>123.37</v>
       </c>
       <c r="N33" t="n">
-        <v>2.53</v>
+        <v>6.54</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T33" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="V33" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0.35</v>
+        <v>1.52</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
       </c>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="inlineStr"/>
-      <c r="AC33" t="inlineStr"/>
-      <c r="AD33" t="inlineStr"/>
-      <c r="AE33" t="inlineStr"/>
-      <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="inlineStr"/>
-      <c r="AH33" t="inlineStr"/>
-      <c r="AI33" t="inlineStr"/>
-      <c r="AJ33" t="inlineStr"/>
-      <c r="AK33" t="inlineStr"/>
-      <c r="AL33" t="inlineStr"/>
-      <c r="AM33" t="inlineStr"/>
-      <c r="AN33" t="inlineStr"/>
-      <c r="AO33" t="inlineStr"/>
-      <c r="AP33" t="inlineStr"/>
-      <c r="AQ33" t="inlineStr"/>
-      <c r="AR33" t="inlineStr"/>
-      <c r="AS33" t="inlineStr"/>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AU33" t="inlineStr"/>
-      <c r="AV33" t="inlineStr"/>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>March 2025: A teacher was killed by ADF.</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>Unspecified Location</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr">
+        <is>
+          <t>Allied Democratic Forces /National Army for the Liberation of Uganda</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>Firearms</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="AW33" t="inlineStr"/>
       <c r="AX33" t="inlineStr"/>
-      <c r="AY33" t="inlineStr"/>
-      <c r="AZ33" t="inlineStr"/>
-      <c r="BA33" t="inlineStr"/>
-      <c r="BB33" t="inlineStr"/>
-      <c r="BC33" t="inlineStr"/>
-      <c r="BD33" t="inlineStr"/>
-      <c r="BE33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Nord-Kivu</t>
+        </is>
+      </c>
+      <c r="AZ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>Nord-Kivu</t>
+        </is>
+      </c>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>Violence against civilians</t>
+        </is>
+      </c>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="BE33" t="inlineStr">
+        <is>
+          <t>ADF: Allied Democratic Forces</t>
+        </is>
+      </c>
       <c r="BF33" t="inlineStr"/>
-      <c r="BG33" t="inlineStr"/>
-      <c r="BH33" t="inlineStr"/>
-      <c r="BI33" t="inlineStr"/>
-      <c r="BJ33" t="inlineStr"/>
-      <c r="BK33" t="n">
-        <v>0.007261027795847325</v>
+      <c r="BG33" t="inlineStr">
+        <is>
+          <t>Civilians (Democratic Republic of Congo)</t>
+        </is>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>Teachers (Democratic Republic of Congo)</t>
+        </is>
+      </c>
+      <c r="BI33" t="inlineStr">
+        <is>
+          <t>On 4 March 2025, ADF militants killed a teacher from Kasanga Tuha Institute near Mapera, closest location Matiba (Oicha, Beni).</t>
+        </is>
+      </c>
+      <c r="BJ33" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="BK33" t="inlineStr">
+        <is>
+          <t>Beni</t>
+        </is>
+      </c>
+      <c r="BL33" t="n">
+        <v>0.2517680222194586</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CD6201ZS02</t>
+          <t>CD6107ZS06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -4814,147 +5192,218 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CD6104ZS01</t>
+          <t>CD5405ZS07</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>CD5402ZS03;CD5402ZS06;CD5405ZS09;CD5405ZS12;CD5407ZS06;CD6104ZS01;CD6107ZS05;CD6201ZS02;CD6202ZS01;CD6205ZS01;CD6207ZS01;CD6207ZS02;CD6208ZS04;CD6212ZS03</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>80.7</v>
+        <v>67.5</v>
       </c>
       <c r="I34" t="n">
-        <v>18.1</v>
+        <v>29.7</v>
       </c>
       <c r="J34" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L34" t="n">
-        <v>19.3</v>
+        <v>32.5</v>
       </c>
       <c r="M34" t="n">
-        <v>89.70999999999999</v>
+        <v>123.37</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>6.54</v>
       </c>
       <c r="O34" t="n">
-        <v>0.71</v>
+        <v>1.19</v>
       </c>
       <c r="P34" t="n">
-        <v>0.58</v>
+        <v>2.33</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="S34" t="n">
-        <v>5.67</v>
+        <v>3.16</v>
       </c>
       <c r="T34" t="n">
-        <v>0.58</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
       </c>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr"/>
-      <c r="AB34" t="inlineStr"/>
-      <c r="AC34" t="inlineStr"/>
-      <c r="AD34" t="inlineStr"/>
-      <c r="AE34" t="inlineStr"/>
-      <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="inlineStr"/>
-      <c r="AH34" t="inlineStr"/>
-      <c r="AI34" t="inlineStr"/>
-      <c r="AJ34" t="inlineStr"/>
-      <c r="AK34" t="inlineStr"/>
-      <c r="AL34" t="inlineStr"/>
-      <c r="AM34" t="inlineStr"/>
-      <c r="AN34" t="inlineStr"/>
-      <c r="AO34" t="inlineStr"/>
-      <c r="AP34" t="inlineStr"/>
-      <c r="AQ34" t="inlineStr"/>
-      <c r="AR34" t="inlineStr"/>
-      <c r="AS34" t="inlineStr"/>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AU34" t="inlineStr"/>
-      <c r="AV34" t="inlineStr"/>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>March 2025: A teacher was killed by ADF.</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>Unspecified Location</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr">
+        <is>
+          <t>Allied Democratic Forces /National Army for the Liberation of Uganda</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>Firearms</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="AW34" t="inlineStr"/>
       <c r="AX34" t="inlineStr"/>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>Sud-Kivu</t>
-        </is>
-      </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>Bukavu</t>
-        </is>
+          <t>Nord-Kivu</t>
+        </is>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>Nord-Kivu</t>
+        </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>Strategic developments ---- Protests ---- Protests ---- Riots ---- Riots ---- Protests</t>
+          <t>Violence against civilians</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>Other ---- Peaceful protest ---- Peaceful protest ---- Violent demonstration ---- Violent demonstration ---- Peaceful protest</t>
+          <t>Abduction/forced disappearance</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>Civilians (Democratic Republic of Congo) ---- Protesters (Democratic Republic of Congo) ---- Protesters (Democratic Republic of Congo) ---- Rioters (Democratic Republic of Congo) ---- Rioters (Democratic Republic of Congo) ---- Protesters (Democratic Republic of Congo)</t>
-        </is>
-      </c>
-      <c r="BF34" t="inlineStr">
-        <is>
-          <t>Teachers (Democratic Republic of Congo) ---- Students (Democratic Republic of Congo) ---- Teachers (Democratic Republic of Congo) ---- Students (Democratic Republic of Congo) ---- Bafuliru Ethnic Group (Democratic Republic of Congo); Students (Democratic Republic of Congo) ---- Catholic Christian Group (Democratic Republic of Congo); SYNECAT: National Union of Teachers of Catholic Convention Schools; Teachers (Democratic Republic of Congo)</t>
-        </is>
-      </c>
-      <c r="BG34" t="inlineStr"/>
-      <c r="BH34" t="inlineStr"/>
+          <t>Unidentified Armed Group (Democratic Republic of Congo)</t>
+        </is>
+      </c>
+      <c r="BF34" t="inlineStr"/>
+      <c r="BG34" t="inlineStr">
+        <is>
+          <t>Civilians (Democratic Republic of Congo)</t>
+        </is>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>Teachers (Democratic Republic of Congo)</t>
+        </is>
+      </c>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>Other: On 7 February 2025, the schools and universities closed for one day in Bukavu (Bukavu, Sud-Kivu) due to the security concerns as M23-RDF were approaching Bukavu. The urban football alliance also suspended the local championship. ---- On 14 October 2024, primary school students protested in Bukavu (Ibanda, Bukavu, Sud-Kivu), to demand the resumption of classes amidst the nationwide teachers' strike. ---- On 14 October 2024, teachers held a sit-in in front of the office of the Sous-Division Educationnelle EPST Bukavu 1, in Bukavu (Ibanda, Bukavu, Sud-Kivu), to protest against 'threats' proclaimed by authorities in the face of the nationwide teachers' strike. ---- Around 1 May 2024 (as reported), students of the of the higher pedagogical institute of Bukavu barricaded roads in Bukavu (Ibanda, Bukavu, Sud-Kivu) to demand the release of their Director General kidnapped since 27 April ---- On 27 April 2024, youth, including students and representatives of the Bafuliru community, demonstrated in Bukavu (Bukavu, Sud-Kivu) to demand the release of the director of ISP Bukavu and his wife who were abducted earlier (coded separately). Some demonstrators burned tires. ---- On 23 February 2024, SYNECAT teachers union staged a sit-in in front of FNB Bank in Bukavu (Ibanda, Bukavu, Sud-Kivu) over the non-payment of their salaries.</t>
+          <t>On 11 August 2024, an unidentified armed group abducted the prefect of Tuendeleye High School in Mabasele (Beni, Nord-Kivu).</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr">
         <is>
-          <t>07 February 2025 ---- 14 October 2024 ---- 14 October 2024 ---- 01 May 2024 ---- 27 April 2024 ---- 23 February 2024</t>
-        </is>
-      </c>
-      <c r="BK34" t="n">
-        <v>0.003004401041525694</v>
+          <t>2024-08-11</t>
+        </is>
+      </c>
+      <c r="BK34" t="inlineStr">
+        <is>
+          <t>Bordj Badji Mokhtar</t>
+        </is>
+      </c>
+      <c r="BL34" t="n">
+        <v>0.2517680222194586</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CD6201ZS03</t>
+          <t>CD6201ZS01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -4963,34 +5412,34 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CD6207ZS04</t>
+          <t>CD6202ZS04</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>CD000ZS00;CD6201ZS03;CD6207ZS04</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>70.2</v>
+        <v>67.5</v>
       </c>
       <c r="I35" t="n">
-        <v>29.8</v>
+        <v>31.8</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L35" t="n">
-        <v>29.8</v>
+        <v>32.5</v>
       </c>
       <c r="M35" t="n">
-        <v>69.39</v>
+        <v>71.69999999999999</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5008,16 +5457,16 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
@@ -5060,14 +5509,15 @@
       <c r="BH35" t="inlineStr"/>
       <c r="BI35" t="inlineStr"/>
       <c r="BJ35" t="inlineStr"/>
-      <c r="BK35" t="n">
-        <v>0.001566742569590589</v>
+      <c r="BK35" t="inlineStr"/>
+      <c r="BL35" t="n">
+        <v>0.007261027795847325</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CD6202ZS01</t>
+          <t>CD6201ZS02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -5076,52 +5526,52 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CD6107ZS05</t>
+          <t>CD6104ZS01</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>CD5402ZS03;CD5402ZS06;CD5405ZS09;CD5405ZS12;CD5407ZS06;CD6104ZS01;CD6107ZS05;CD6201ZS02;CD6202ZS01;CD6205ZS01;CD6207ZS01;CD6207ZS02;CD6208ZS04;CD6212ZS03</t>
+          <t>CD5402ZS03;CD5402ZS06;CD5405ZS12;CD5407ZS06;CD6104ZS01;CD6107ZS05;CD6201ZS02;CD6202ZS01;CD6205ZS01;CD6207ZS01;CD6207ZS02;CD6208ZS04;CD6212ZS03</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>59.6</v>
+        <v>80.7</v>
       </c>
       <c r="I36" t="n">
-        <v>38.4</v>
+        <v>18.1</v>
       </c>
       <c r="J36" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>40.4</v>
+        <v>19.3</v>
       </c>
       <c r="M36" t="n">
-        <v>136.13</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="P36" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>3.17</v>
+        <v>5.67</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -5130,7 +5580,7 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
@@ -5161,26 +5611,67 @@
       <c r="AV36" t="inlineStr"/>
       <c r="AW36" t="inlineStr"/>
       <c r="AX36" t="inlineStr"/>
-      <c r="AY36" t="inlineStr"/>
-      <c r="AZ36" t="inlineStr"/>
-      <c r="BA36" t="inlineStr"/>
-      <c r="BB36" t="inlineStr"/>
-      <c r="BC36" t="inlineStr"/>
-      <c r="BD36" t="inlineStr"/>
-      <c r="BE36" t="inlineStr"/>
-      <c r="BF36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Sud-Kivu</t>
+        </is>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>Sud-Kivu</t>
+        </is>
+      </c>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>Protests ---- Riots ---- Riots ---- Protests ---- Protests ---- Strategic developments</t>
+        </is>
+      </c>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>Peaceful protest ---- Violent demonstration ---- Violent demonstration ---- Peaceful protest ---- Peaceful protest ---- Other</t>
+        </is>
+      </c>
+      <c r="BE36" t="inlineStr">
+        <is>
+          <t>Protesters (Democratic Republic of Congo) ---- Rioters (Democratic Republic of Congo) ---- Rioters (Democratic Republic of Congo) ---- Protesters (Democratic Republic of Congo) ---- Protesters (Democratic Republic of Congo) ---- Civilians (Democratic Republic of Congo)</t>
+        </is>
+      </c>
+      <c r="BF36" t="inlineStr">
+        <is>
+          <t>Catholic Christian Group (Democratic Republic of Congo); SYNECAT: National Union of Teachers of Catholic Convention Schools; Teachers (Democratic Republic of Congo) ---- Bafuliru Ethnic Group (Democratic Republic of Congo); Students (Democratic Republic of Congo) ---- Students (Democratic Republic of Congo) ---- Students (Democratic Republic of Congo) ---- Teachers (Democratic Republic of Congo) ---- Teachers (Democratic Republic of Congo)</t>
+        </is>
+      </c>
       <c r="BG36" t="inlineStr"/>
       <c r="BH36" t="inlineStr"/>
-      <c r="BI36" t="inlineStr"/>
-      <c r="BJ36" t="inlineStr"/>
-      <c r="BK36" t="n">
-        <v>0.001020727007603375</v>
+      <c r="BI36" t="inlineStr">
+        <is>
+          <t>On 23 February 2024, SYNECAT teachers union staged a sit-in in front of FNB Bank in Bukavu (Ibanda, Bukavu, Sud-Kivu) over the non-payment of their salaries. ---- On 27 April 2024, youth, including students and representatives of the Bafuliru community, demonstrated in Bukavu (Bukavu, Sud-Kivu) to demand the release of the director of ISP Bukavu and his wife who were abducted earlier (coded separately). Some demonstrators burned tires. ---- Around 1 May 2024 (as reported), students of the of the higher pedagogical institute of Bukavu barricaded roads in Bukavu (Ibanda, Bukavu, Sud-Kivu) to demand the release of their Director General kidnapped since 27 April ---- On 14 October 2024, primary school students protested in Bukavu (Ibanda, Bukavu, Sud-Kivu), to demand the resumption of classes amidst the nationwide teachers' strike. ---- On 14 October 2024, teachers held a sit-in in front of the office of the Sous-Division Educationnelle EPST Bukavu 1, in Bukavu (Ibanda, Bukavu, Sud-Kivu), to protest against 'threats' proclaimed by authorities in the face of the nationwide teachers' strike. ---- Other: On 7 February 2025, the schools and universities closed for one day in Bukavu (Bukavu, Sud-Kivu) due to the security concerns as M23-RDF were approaching Bukavu. The urban football alliance also suspended the local championship.</t>
+        </is>
+      </c>
+      <c r="BJ36" t="inlineStr">
+        <is>
+          <t>2024-02-23 ---- 2024-04-27 ---- 2024-05-01 ---- 2024-10-14 ---- 2024-10-14 ---- 2025-02-07</t>
+        </is>
+      </c>
+      <c r="BK36" t="inlineStr">
+        <is>
+          <t>Bukavu</t>
+        </is>
+      </c>
+      <c r="BL36" t="n">
+        <v>0.003004401041525694</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CD6202ZS03</t>
+          <t>CD6201ZS03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -5189,61 +5680,61 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CD5405ZS13</t>
+          <t>CD6207ZS04</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD000ZS00;CD6201ZS03;CD6207ZS04</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>62.3</v>
+        <v>70.2</v>
       </c>
       <c r="I37" t="n">
-        <v>34.1</v>
+        <v>29.8</v>
       </c>
       <c r="J37" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>37.7</v>
+        <v>29.8</v>
       </c>
       <c r="M37" t="n">
-        <v>142.12</v>
+        <v>69.39</v>
       </c>
       <c r="N37" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.49</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>23.39</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
@@ -5286,14 +5777,15 @@
       <c r="BH37" t="inlineStr"/>
       <c r="BI37" t="inlineStr"/>
       <c r="BJ37" t="inlineStr"/>
-      <c r="BK37" t="n">
-        <v>0.07786691835771591</v>
+      <c r="BK37" t="inlineStr"/>
+      <c r="BL37" t="n">
+        <v>0.001566742569590589</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CD6202ZS04</t>
+          <t>CD6202ZS01</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -5302,49 +5794,49 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CD6202ZS05</t>
+          <t>CD6107ZS05</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS03;CD5402ZS06;CD5405ZS12;CD5407ZS06;CD6104ZS01;CD6107ZS05;CD6201ZS02;CD6202ZS01;CD6205ZS01;CD6207ZS01;CD6207ZS02;CD6208ZS04;CD6212ZS03</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>68.90000000000001</v>
+        <v>59.6</v>
       </c>
       <c r="I38" t="n">
-        <v>29.9</v>
+        <v>38.4</v>
       </c>
       <c r="J38" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="K38" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>31.1</v>
+        <v>40.4</v>
       </c>
       <c r="M38" t="n">
-        <v>80.98</v>
+        <v>136.13</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="O38" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -5353,10 +5845,10 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>0.31</v>
+        <v>1.89</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
@@ -5387,26 +5879,67 @@
       <c r="AV38" t="inlineStr"/>
       <c r="AW38" t="inlineStr"/>
       <c r="AX38" t="inlineStr"/>
-      <c r="AY38" t="inlineStr"/>
-      <c r="AZ38" t="inlineStr"/>
-      <c r="BA38" t="inlineStr"/>
-      <c r="BB38" t="inlineStr"/>
-      <c r="BC38" t="inlineStr"/>
-      <c r="BD38" t="inlineStr"/>
-      <c r="BE38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Sud-Kivu</t>
+        </is>
+      </c>
+      <c r="AZ38" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB38" t="inlineStr">
+        <is>
+          <t>Sud-Kivu</t>
+        </is>
+      </c>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>Violence against civilians</t>
+        </is>
+      </c>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="BE38" t="inlineStr">
+        <is>
+          <t>M23: March 23 Movement</t>
+        </is>
+      </c>
       <c r="BF38" t="inlineStr"/>
-      <c r="BG38" t="inlineStr"/>
+      <c r="BG38" t="inlineStr">
+        <is>
+          <t>Civilians (Democratic Republic of Congo)</t>
+        </is>
+      </c>
       <c r="BH38" t="inlineStr"/>
-      <c r="BI38" t="inlineStr"/>
-      <c r="BJ38" t="inlineStr"/>
-      <c r="BK38" t="n">
-        <v>0.01692629054769242</v>
+      <c r="BI38" t="inlineStr">
+        <is>
+          <t>Around 12 July 2025 (between 11 July - 12 July), M23 attacked and killed 5 civilians in Karambi, closest to Kabare (Kabare, Kabare, Sud-Kivu), in retaliation for the killing of one of their members. Victims included suspected Wazalendo affiliates and two teachers. The violence caused mass civilian displacement.</t>
+        </is>
+      </c>
+      <c r="BJ38" t="inlineStr">
+        <is>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="BK38" t="inlineStr">
+        <is>
+          <t>Kabare</t>
+        </is>
+      </c>
+      <c r="BL38" t="n">
+        <v>0.001020727007603375</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CD6202ZS05</t>
+          <t>CD6202ZS03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -5415,61 +5948,61 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CD5405ZS07</t>
+          <t>CD5405ZS13</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>59.8</v>
+        <v>62.3</v>
       </c>
       <c r="I39" t="n">
-        <v>38.1</v>
+        <v>34.1</v>
       </c>
       <c r="J39" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="K39" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="L39" t="n">
-        <v>40.2</v>
+        <v>37.7</v>
       </c>
       <c r="M39" t="n">
-        <v>64.2</v>
+        <v>142.12</v>
       </c>
       <c r="N39" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>23.39</v>
       </c>
       <c r="T39" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W39" t="n">
-        <v>21.17</v>
+        <v>1.91</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -5512,14 +6045,15 @@
       <c r="BH39" t="inlineStr"/>
       <c r="BI39" t="inlineStr"/>
       <c r="BJ39" t="inlineStr"/>
-      <c r="BK39" t="n">
-        <v>0.002737949419987031</v>
+      <c r="BK39" t="inlineStr"/>
+      <c r="BL39" t="n">
+        <v>0.07786691835771591</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CD6205ZS01</t>
+          <t>CD6202ZS04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -5528,40 +6062,40 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CD5407ZS06</t>
+          <t>CD6202ZS05</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>CD5402ZS03;CD5402ZS06;CD5405ZS09;CD5405ZS12;CD5407ZS06;CD6104ZS01;CD6107ZS05;CD6201ZS02;CD6202ZS01;CD6205ZS01;CD6207ZS01;CD6207ZS02;CD6208ZS04;CD6212ZS03</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>68.59999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>22.7</v>
+        <v>29.9</v>
       </c>
       <c r="J40" t="n">
-        <v>8.800000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L40" t="n">
-        <v>31.4</v>
+        <v>31.1</v>
       </c>
       <c r="M40" t="n">
-        <v>90.03</v>
+        <v>80.98</v>
       </c>
       <c r="N40" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>2.43</v>
+        <v>0.61</v>
       </c>
       <c r="P40" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -5570,19 +6104,19 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>14.07</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>7.96</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>2.13</v>
+        <v>0.31</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
@@ -5625,14 +6159,15 @@
       <c r="BH40" t="inlineStr"/>
       <c r="BI40" t="inlineStr"/>
       <c r="BJ40" t="inlineStr"/>
-      <c r="BK40" t="n">
-        <v>0.2377312909535975</v>
+      <c r="BK40" t="inlineStr"/>
+      <c r="BL40" t="n">
+        <v>0.01692629054769242</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CD6205ZS02</t>
+          <t>CD6202ZS05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -5641,40 +6176,40 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CD5407ZS05</t>
+          <t>CD5405ZS07</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>66.2</v>
+        <v>59.8</v>
       </c>
       <c r="I41" t="n">
-        <v>26.2</v>
+        <v>38.1</v>
       </c>
       <c r="J41" t="n">
-        <v>5.1</v>
+        <v>1.7</v>
       </c>
       <c r="K41" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="L41" t="n">
-        <v>33.8</v>
+        <v>40.2</v>
       </c>
       <c r="M41" t="n">
-        <v>138.4</v>
+        <v>64.2</v>
       </c>
       <c r="N41" t="n">
-        <v>7.37</v>
+        <v>1.02</v>
       </c>
       <c r="O41" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -5683,19 +6218,19 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>20.05</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>6.67</v>
+        <v>0.68</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>12.98</v>
+        <v>21.17</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
@@ -5726,62 +6261,27 @@
       <c r="AV41" t="inlineStr"/>
       <c r="AW41" t="inlineStr"/>
       <c r="AX41" t="inlineStr"/>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>Sud-Kivu</t>
-        </is>
-      </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>Kalehe</t>
-        </is>
-      </c>
-      <c r="BA41" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC41" t="inlineStr">
-        <is>
-          <t>Battles</t>
-        </is>
-      </c>
-      <c r="BD41" t="inlineStr">
-        <is>
-          <t>Armed clash</t>
-        </is>
-      </c>
-      <c r="BE41" t="inlineStr">
-        <is>
-          <t>M23: March 23 Movement</t>
-        </is>
-      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr"/>
+      <c r="BA41" t="inlineStr"/>
+      <c r="BB41" t="inlineStr"/>
+      <c r="BC41" t="inlineStr"/>
+      <c r="BD41" t="inlineStr"/>
+      <c r="BE41" t="inlineStr"/>
       <c r="BF41" t="inlineStr"/>
-      <c r="BG41" t="inlineStr">
-        <is>
-          <t>EPLC: Awakening of Patriots for the Liberation of Congo (Wazalendo)</t>
-        </is>
-      </c>
+      <c r="BG41" t="inlineStr"/>
       <c r="BH41" t="inlineStr"/>
-      <c r="BI41" t="inlineStr">
-        <is>
-          <t>On 7 April 2025, M23 clashed against Wazalendo and pushed them back in Bashuku, coded to nearby (10 km) Kalehe (Kalehe, Sud-Kivu), Katale, Kafulula, and surroundings (coded separately). Unspecified number of fatalities coded as 3. Schools were closed following the clashes in Kalehe and Ihusi. Civilians were looted.</t>
-        </is>
-      </c>
-      <c r="BJ41" t="inlineStr">
-        <is>
-          <t>07 April 2025</t>
-        </is>
-      </c>
-      <c r="BK41" t="n">
-        <v>0.2623185277133143</v>
+      <c r="BI41" t="inlineStr"/>
+      <c r="BJ41" t="inlineStr"/>
+      <c r="BK41" t="inlineStr"/>
+      <c r="BL41" t="n">
+        <v>0.002737949419987031</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CD6205ZS03</t>
+          <t>CD6205ZS01</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -5790,61 +6290,61 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CD6202ZS03</t>
+          <t>CD5407ZS06</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS03;CD5402ZS06;CD5405ZS12;CD5407ZS06;CD6104ZS01;CD6107ZS05;CD6201ZS02;CD6202ZS01;CD6205ZS01;CD6207ZS01;CD6207ZS02;CD6208ZS04;CD6212ZS03</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>58.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>34.5</v>
+        <v>22.7</v>
       </c>
       <c r="J42" t="n">
-        <v>5.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>41.7</v>
+        <v>31.4</v>
       </c>
       <c r="M42" t="n">
-        <v>103.22</v>
+        <v>90.03</v>
       </c>
       <c r="N42" t="n">
-        <v>20.25</v>
+        <v>1.37</v>
       </c>
       <c r="O42" t="n">
-        <v>0.59</v>
+        <v>2.43</v>
       </c>
       <c r="P42" t="n">
-        <v>0.59</v>
+        <v>1.06</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>11.9</v>
+        <v>14.07</v>
       </c>
       <c r="T42" t="n">
-        <v>0.59</v>
+        <v>7.96</v>
       </c>
       <c r="U42" t="n">
-        <v>0.59</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="W42" t="n">
-        <v>22.23</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -5887,14 +6387,15 @@
       <c r="BH42" t="inlineStr"/>
       <c r="BI42" t="inlineStr"/>
       <c r="BJ42" t="inlineStr"/>
-      <c r="BK42" t="n">
-        <v>0.03248203741907946</v>
+      <c r="BK42" t="inlineStr"/>
+      <c r="BL42" t="n">
+        <v>0.2377312909535975</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CD6205ZS04</t>
+          <t>CD6205ZS02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -5903,61 +6404,61 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CD5405ZS05</t>
+          <t>CD5407ZS05</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>40.8</v>
+        <v>66.2</v>
       </c>
       <c r="I43" t="n">
-        <v>36.2</v>
+        <v>26.2</v>
       </c>
       <c r="J43" t="n">
-        <v>13.9</v>
+        <v>5.1</v>
       </c>
       <c r="K43" t="n">
-        <v>9</v>
+        <v>2.5</v>
       </c>
       <c r="L43" t="n">
-        <v>59.2</v>
+        <v>33.8</v>
       </c>
       <c r="M43" t="n">
-        <v>103.52</v>
+        <v>138.4</v>
       </c>
       <c r="N43" t="n">
-        <v>5.61</v>
+        <v>7.37</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="P43" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>16.65</v>
+        <v>20.05</v>
       </c>
       <c r="T43" t="n">
-        <v>0.36</v>
+        <v>6.67</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0.93</v>
+        <v>1.48</v>
       </c>
       <c r="W43" t="n">
-        <v>18.83</v>
+        <v>12.98</v>
       </c>
       <c r="X43" t="n">
         <v>0</v>
@@ -5993,57 +6494,62 @@
           <t>Sud-Kivu</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>Kalehe</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>3</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB43" t="n">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>Sud-Kivu</t>
+        </is>
       </c>
       <c r="BC43" t="inlineStr">
         <is>
-          <t>Strategic developments ---- Strategic developments ---- Strategic developments ---- Strategic developments ---- Explosions/Remote violence ---- Strategic developments</t>
+          <t>Battles</t>
         </is>
       </c>
       <c r="BD43" t="inlineStr">
         <is>
-          <t>Other ---- Other ---- Other ---- Other ---- Shelling/artillery/missile attack ---- Other</t>
+          <t>Armed clash</t>
         </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
-          <t>Civilians (Democratic Republic of Congo) ---- Civilians (Democratic Republic of Congo) ---- Civilians (Democratic Republic of Congo) ---- M23: March 23 Movement ---- M23: March 23 Movement ---- Civilians (Democratic Republic of Congo)</t>
-        </is>
-      </c>
-      <c r="BF43" t="inlineStr">
-        <is>
-          <t>Refugees/IDPs (Democratic Republic of Congo) ---- Refugees/IDPs (Democratic Republic of Congo) ---- Refugees/IDPs (Democratic Republic of Congo) ---- Refugees/IDPs (Democratic Republic of Congo)</t>
-        </is>
-      </c>
-      <c r="BG43" t="inlineStr"/>
+          <t>M23: March 23 Movement</t>
+        </is>
+      </c>
+      <c r="BF43" t="inlineStr"/>
+      <c r="BG43" t="inlineStr">
+        <is>
+          <t>EPLC: Awakening of Patriots for the Liberation of Congo (Wazalendo)</t>
+        </is>
+      </c>
       <c r="BH43" t="inlineStr"/>
       <c r="BI43" t="inlineStr">
         <is>
-          <t>Displacement: Around 26 January 2025 (as reported), civilians fled in Bweremana (Buhavu, Kalehe, Sud-Kivu) in mass to take shelter in schools and areas they hope are safe following the clashes following clashes between M23/RDF and FARDC and their allies (coded separately). ---- Displacement: Around 26 January 2025 (as reported), civilians fled in Kalungu (Buhavu, Kalehe, Sud-Kivu) in mass to take shelter in schools and areas they hope are safe following the clashes with M23 militants, Rwandan forces, and FARDC and their allies (coded separately). ---- Displacement: Around 26 January 2025 (as reported), civilians fled in Minova (Buhavu, Kalehe, Sud-Kivu) in mass to take shelter in schools and areas they hope are safe following clashes with M23 militants, Rwandan forces, and FARDC and their allies (coded separately). ---- Other: Around 20 January 2025 (as reported), M23 occupied schools, and hospitals, forced IDPs out of camps and subjected the civilian population to forced conscription and forced labor in Minova (Kalehe, Sud-Kivu). ---- On 23 May 2024, M23 fired 3 bombs, one on the Catholic parish in Bobandana neighborhood, the second in near the Mwanga school complex in Ludahuba neighborhood, and the third in Bugeri neigborhood, in Minova (Kalehe, Sud-Kivu). No casualties. ---- Displacement: On 6 February 2024, hundreds of displaced persons from Masisi territory arrived in Minova (Kalehe, Sud-Kivu) after fleeing clashes between Wazalendo and M23 supported by the RDF. These displaced persons came from several villages including Kirotshe, Shasha, Bweremana, Mwamubingwa, Kituva, Nguba, Kiluku, Kihindo and settled in schools, churches, and hospitals.</t>
+          <t>On 7 April 2025, M23 clashed against Wazalendo and pushed them back in Bashuku, coded to nearby (10 km) Kalehe (Kalehe, Sud-Kivu), Katale, Kafulula, and surroundings (coded separately). Unspecified number of fatalities coded as 3. Schools were closed following the clashes in Kalehe and Ihusi. Civilians were looted.</t>
         </is>
       </c>
       <c r="BJ43" t="inlineStr">
         <is>
-          <t>26 January 2025 ---- 26 January 2025 ---- 26 January 2025 ---- 20 January 2025 ---- 23 May 2024 ---- 06 February 2024</t>
-        </is>
-      </c>
-      <c r="BK43" t="n">
-        <v>0.6655632958110352</v>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="BK43" t="inlineStr">
+        <is>
+          <t>Kalehe</t>
+        </is>
+      </c>
+      <c r="BL43" t="n">
+        <v>0.2623185277133143</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CD6207ZS01</t>
+          <t>CD6205ZS03</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -6052,61 +6558,61 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CD6104ZS01</t>
+          <t>CD6202ZS03</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>CD5402ZS03;CD5402ZS06;CD5405ZS09;CD5405ZS12;CD5407ZS06;CD6104ZS01;CD6107ZS05;CD6201ZS02;CD6202ZS01;CD6205ZS01;CD6207ZS01;CD6207ZS02;CD6208ZS04;CD6212ZS03</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>72.7</v>
+        <v>58.3</v>
       </c>
       <c r="I44" t="n">
-        <v>25.8</v>
+        <v>34.5</v>
       </c>
       <c r="J44" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="K44" t="n">
         <v>1.5</v>
       </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
       <c r="L44" t="n">
-        <v>27.3</v>
+        <v>41.7</v>
       </c>
       <c r="M44" t="n">
-        <v>68</v>
+        <v>103.22</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>20.25</v>
       </c>
       <c r="O44" t="n">
-        <v>0.91</v>
+        <v>0.59</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.45</v>
+        <v>1.78</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>3.3</v>
+        <v>11.9</v>
       </c>
       <c r="T44" t="n">
-        <v>1.1</v>
+        <v>0.59</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>22.23</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
@@ -6149,14 +6655,15 @@
       <c r="BH44" t="inlineStr"/>
       <c r="BI44" t="inlineStr"/>
       <c r="BJ44" t="inlineStr"/>
-      <c r="BK44" t="n">
-        <v>0.04394571632645389</v>
+      <c r="BK44" t="inlineStr"/>
+      <c r="BL44" t="n">
+        <v>0.03248203741907946</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CD6207ZS02</t>
+          <t>CD6205ZS04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -6165,61 +6672,61 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CD6104ZS01</t>
+          <t>CD5405ZS05</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>CD5402ZS03;CD5402ZS06;CD5405ZS09;CD5405ZS12;CD5407ZS06;CD6104ZS01;CD6107ZS05;CD6201ZS02;CD6202ZS01;CD6205ZS01;CD6207ZS01;CD6207ZS02;CD6208ZS04;CD6212ZS03</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>55</v>
+        <v>40.8</v>
       </c>
       <c r="I45" t="n">
-        <v>43.2</v>
+        <v>36.2</v>
       </c>
       <c r="J45" t="n">
-        <v>1.8</v>
+        <v>13.9</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L45" t="n">
-        <v>45</v>
+        <v>59.2</v>
       </c>
       <c r="M45" t="n">
-        <v>124.81</v>
+        <v>103.52</v>
       </c>
       <c r="N45" t="n">
-        <v>1.23</v>
+        <v>5.61</v>
       </c>
       <c r="O45" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0.41</v>
+        <v>0.73</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.62</v>
+        <v>1.19</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>13.75</v>
+        <v>16.65</v>
       </c>
       <c r="T45" t="n">
-        <v>3.82</v>
+        <v>0.36</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>18.83</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -6250,26 +6757,67 @@
       <c r="AV45" t="inlineStr"/>
       <c r="AW45" t="inlineStr"/>
       <c r="AX45" t="inlineStr"/>
-      <c r="AY45" t="inlineStr"/>
-      <c r="AZ45" t="inlineStr"/>
-      <c r="BA45" t="inlineStr"/>
-      <c r="BB45" t="inlineStr"/>
-      <c r="BC45" t="inlineStr"/>
-      <c r="BD45" t="inlineStr"/>
-      <c r="BE45" t="inlineStr"/>
-      <c r="BF45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Sud-Kivu</t>
+        </is>
+      </c>
+      <c r="AZ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>Sud-Kivu</t>
+        </is>
+      </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>Strategic developments ---- Explosions/Remote violence ---- Strategic developments ---- Strategic developments ---- Strategic developments ---- Strategic developments</t>
+        </is>
+      </c>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>Other ---- Shelling/artillery/missile attack ---- Other ---- Other ---- Other ---- Other</t>
+        </is>
+      </c>
+      <c r="BE45" t="inlineStr">
+        <is>
+          <t>Civilians (Democratic Republic of Congo) ---- M23: March 23 Movement ---- M23: March 23 Movement ---- Civilians (Democratic Republic of Congo) ---- Civilians (Democratic Republic of Congo) ---- Civilians (Democratic Republic of Congo)</t>
+        </is>
+      </c>
+      <c r="BF45" t="inlineStr">
+        <is>
+          <t>Refugees/IDPs (Democratic Republic of Congo) ---- Refugees/IDPs (Democratic Republic of Congo) ---- Refugees/IDPs (Democratic Republic of Congo) ---- Refugees/IDPs (Democratic Republic of Congo)</t>
+        </is>
+      </c>
       <c r="BG45" t="inlineStr"/>
       <c r="BH45" t="inlineStr"/>
-      <c r="BI45" t="inlineStr"/>
-      <c r="BJ45" t="inlineStr"/>
-      <c r="BK45" t="n">
-        <v>0.04006506292269497</v>
+      <c r="BI45" t="inlineStr">
+        <is>
+          <t>Displacement: On 6 February 2024, hundreds of displaced persons from Masisi territory arrived in Minova (Kalehe, Sud-Kivu) after fleeing clashes between Wazalendo and M23 supported by the RDF. These displaced persons came from several villages including Kirotshe, Shasha, Bweremana, Mwamubingwa, Kituva, Nguba, Kiluku, Kihindo and settled in schools, churches, and hospitals. ---- On 23 May 2024, M23 fired 3 bombs, one on the Catholic parish in Bobandana neighborhood, the second in near the Mwanga school complex in Ludahuba neighborhood, and the third in Bugeri neigborhood, in Minova (Kalehe, Sud-Kivu). No casualties. ---- Other: Around 20 January 2025 (as reported), M23 occupied schools, and hospitals, forced IDPs out of camps and subjected the civilian population to forced conscription and forced labor in Minova (Kalehe, Sud-Kivu). ---- Displacement: Around 26 January 2025 (as reported), civilians fled in Bweremana (Buhavu, Kalehe, Sud-Kivu) in mass to take shelter in schools and areas they hope are safe following the clashes following clashes between M23/RDF and FARDC and their allies (coded separately). ---- Displacement: Around 26 January 2025 (as reported), civilians fled in Minova (Buhavu, Kalehe, Sud-Kivu) in mass to take shelter in schools and areas they hope are safe following clashes with M23 militants, Rwandan forces, and FARDC and their allies (coded separately). ---- Displacement: Around 26 January 2025 (as reported), civilians fled in Kalungu (Buhavu, Kalehe, Sud-Kivu) in mass to take shelter in schools and areas they hope are safe following the clashes with M23 militants, Rwandan forces, and FARDC and their allies (coded separately).</t>
+        </is>
+      </c>
+      <c r="BJ45" t="inlineStr">
+        <is>
+          <t>2024-02-06 ---- 2024-05-23 ---- 2025-01-20 ---- 2025-01-26 ---- 2025-01-26 ---- 2025-01-26</t>
+        </is>
+      </c>
+      <c r="BK45" t="inlineStr">
+        <is>
+          <t>Kalehe</t>
+        </is>
+      </c>
+      <c r="BL45" t="n">
+        <v>0.6655632958110352</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CD6207ZS03</t>
+          <t>CD6207ZS01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -6278,61 +6826,61 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CD5403ZS02</t>
+          <t>CD6104ZS01</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS03;CD5402ZS06;CD5405ZS12;CD5407ZS06;CD6104ZS01;CD6107ZS05;CD6201ZS02;CD6202ZS01;CD6205ZS01;CD6207ZS01;CD6207ZS02;CD6208ZS04;CD6212ZS03</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>65.90000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="I46" t="n">
-        <v>27.7</v>
+        <v>25.8</v>
       </c>
       <c r="J46" t="n">
-        <v>5.6</v>
+        <v>1.5</v>
       </c>
       <c r="K46" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>34.1</v>
+        <v>27.3</v>
       </c>
       <c r="M46" t="n">
-        <v>86.93000000000001</v>
+        <v>68</v>
       </c>
       <c r="N46" t="n">
-        <v>14.65</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>1.52</v>
+        <v>0.91</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.86</v>
+        <v>0.45</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
         <v>0</v>
@@ -6375,14 +6923,15 @@
       <c r="BH46" t="inlineStr"/>
       <c r="BI46" t="inlineStr"/>
       <c r="BJ46" t="inlineStr"/>
-      <c r="BK46" t="n">
-        <v>0.03570114660616838</v>
+      <c r="BK46" t="inlineStr"/>
+      <c r="BL46" t="n">
+        <v>0.04394571632645389</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CD6207ZS04</t>
+          <t>CD6207ZS02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -6391,52 +6940,52 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CD000ZS00</t>
+          <t>CD6104ZS01</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>CD000ZS00;CD6201ZS03;CD6207ZS04</t>
+          <t>CD5402ZS03;CD5402ZS06;CD5405ZS12;CD5407ZS06;CD6104ZS01;CD6107ZS05;CD6201ZS02;CD6202ZS01;CD6205ZS01;CD6207ZS01;CD6207ZS02;CD6208ZS04;CD6212ZS03</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>58.2</v>
+        <v>55</v>
       </c>
       <c r="I47" t="n">
-        <v>41.8</v>
+        <v>43.2</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>41.8</v>
+        <v>45</v>
       </c>
       <c r="M47" t="n">
-        <v>149.32</v>
+        <v>124.81</v>
       </c>
       <c r="N47" t="n">
-        <v>0.48</v>
+        <v>1.23</v>
       </c>
       <c r="O47" t="n">
-        <v>0.48</v>
+        <v>1.18</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="R47" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>13.75</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -6488,14 +7037,15 @@
       <c r="BH47" t="inlineStr"/>
       <c r="BI47" t="inlineStr"/>
       <c r="BJ47" t="inlineStr"/>
-      <c r="BK47" t="n">
-        <v>0.02181869743617012</v>
+      <c r="BK47" t="inlineStr"/>
+      <c r="BL47" t="n">
+        <v>0.04006506292269497</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CD6208ZS02</t>
+          <t>CD6207ZS03</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -6504,43 +7054,43 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CD5405ZS13</t>
+          <t>CD5403ZS02</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>77.90000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>19.8</v>
+        <v>27.7</v>
       </c>
       <c r="J48" t="n">
-        <v>1.2</v>
+        <v>5.6</v>
       </c>
       <c r="K48" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="L48" t="n">
-        <v>22.1</v>
+        <v>34.1</v>
       </c>
       <c r="M48" t="n">
-        <v>62.5</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="N48" t="n">
-        <v>1.34</v>
+        <v>14.65</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -6555,10 +7105,10 @@
         <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="W48" t="n">
-        <v>1.34</v>
+        <v>0.76</v>
       </c>
       <c r="X48" t="n">
         <v>0</v>
@@ -6589,66 +7139,27 @@
       <c r="AV48" t="inlineStr"/>
       <c r="AW48" t="inlineStr"/>
       <c r="AX48" t="inlineStr"/>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t>Sud-Kivu</t>
-        </is>
-      </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>Uvira</t>
-        </is>
-      </c>
-      <c r="BA48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB48" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC48" t="inlineStr">
-        <is>
-          <t>Violence against civilians</t>
-        </is>
-      </c>
-      <c r="BD48" t="inlineStr">
-        <is>
-          <t>Abduction/forced disappearance</t>
-        </is>
-      </c>
-      <c r="BE48" t="inlineStr">
-        <is>
-          <t>Unidentified Armed Group (Democratic Republic of Congo)</t>
-        </is>
-      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr"/>
+      <c r="BA48" t="inlineStr"/>
+      <c r="BB48" t="inlineStr"/>
+      <c r="BC48" t="inlineStr"/>
+      <c r="BD48" t="inlineStr"/>
+      <c r="BE48" t="inlineStr"/>
       <c r="BF48" t="inlineStr"/>
-      <c r="BG48" t="inlineStr">
-        <is>
-          <t>Civilians (Democratic Republic of Congo)</t>
-        </is>
-      </c>
-      <c r="BH48" t="inlineStr">
-        <is>
-          <t>Protestant Christian Group (Democratic Republic of Congo); Teachers (Democratic Republic of Congo)</t>
-        </is>
-      </c>
-      <c r="BI48" t="inlineStr">
-        <is>
-          <t>On 27 April 2024, unidentified armed men abducted the head of Bukavu's ISP (Higher Teaching Institute) and a woman, the spouse of the man, in Luberizi (Ruzizi, Uvira, Sud-Kivu). The director is also a Pentecostal pastor and a former MP. Youth protested to demand their release (coded separately). The abductees were released on 29 April 2024. No further details on their release.</t>
-        </is>
-      </c>
-      <c r="BJ48" t="inlineStr">
-        <is>
-          <t>27 April 2024</t>
-        </is>
-      </c>
-      <c r="BK48" t="n">
-        <v>0.1000427476021267</v>
+      <c r="BG48" t="inlineStr"/>
+      <c r="BH48" t="inlineStr"/>
+      <c r="BI48" t="inlineStr"/>
+      <c r="BJ48" t="inlineStr"/>
+      <c r="BK48" t="inlineStr"/>
+      <c r="BL48" t="n">
+        <v>0.03570114660616838</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CD6208ZS03</t>
+          <t>CD6207ZS04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -6657,37 +7168,37 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CD6208ZS02</t>
+          <t>CD000ZS00</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD000ZS00;CD6201ZS03;CD6207ZS04</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>77.7</v>
+        <v>58.2</v>
       </c>
       <c r="I49" t="n">
-        <v>20</v>
+        <v>41.8</v>
       </c>
       <c r="J49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>22.3</v>
+        <v>41.8</v>
       </c>
       <c r="M49" t="n">
-        <v>80.81</v>
+        <v>149.32</v>
       </c>
       <c r="N49" t="n">
-        <v>6</v>
+        <v>0.48</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
@@ -6696,7 +7207,7 @@
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -6711,7 +7222,7 @@
         <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
         <v>0</v>
@@ -6754,14 +7265,15 @@
       <c r="BH49" t="inlineStr"/>
       <c r="BI49" t="inlineStr"/>
       <c r="BJ49" t="inlineStr"/>
-      <c r="BK49" t="n">
-        <v>0.06883975686326899</v>
+      <c r="BK49" t="inlineStr"/>
+      <c r="BL49" t="n">
+        <v>0.02181869743617012</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CD6208ZS04</t>
+          <t>CD6208ZS02</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -6770,34 +7282,34 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CD5407ZS06</t>
+          <t>CD5405ZS13</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>CD5402ZS03;CD5402ZS06;CD5405ZS09;CD5405ZS12;CD5407ZS06;CD6104ZS01;CD6107ZS05;CD6201ZS02;CD6202ZS01;CD6205ZS01;CD6207ZS01;CD6207ZS02;CD6208ZS04;CD6212ZS03</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>79.09999999999999</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>20.2</v>
+        <v>19.8</v>
       </c>
       <c r="J50" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="L50" t="n">
-        <v>20.9</v>
+        <v>22.1</v>
       </c>
       <c r="M50" t="n">
-        <v>66.03999999999999</v>
+        <v>62.5</v>
       </c>
       <c r="N50" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6824,7 +7336,7 @@
         <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X50" t="n">
         <v>0</v>
@@ -6855,26 +7367,71 @@
       <c r="AV50" t="inlineStr"/>
       <c r="AW50" t="inlineStr"/>
       <c r="AX50" t="inlineStr"/>
-      <c r="AY50" t="inlineStr"/>
-      <c r="AZ50" t="inlineStr"/>
-      <c r="BA50" t="inlineStr"/>
-      <c r="BB50" t="inlineStr"/>
-      <c r="BC50" t="inlineStr"/>
-      <c r="BD50" t="inlineStr"/>
-      <c r="BE50" t="inlineStr"/>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Sud-Kivu</t>
+        </is>
+      </c>
+      <c r="AZ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB50" t="inlineStr">
+        <is>
+          <t>Sud-Kivu</t>
+        </is>
+      </c>
+      <c r="BC50" t="inlineStr">
+        <is>
+          <t>Violence against civilians</t>
+        </is>
+      </c>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>Abduction/forced disappearance</t>
+        </is>
+      </c>
+      <c r="BE50" t="inlineStr">
+        <is>
+          <t>Unidentified Armed Group (Democratic Republic of Congo)</t>
+        </is>
+      </c>
       <c r="BF50" t="inlineStr"/>
-      <c r="BG50" t="inlineStr"/>
-      <c r="BH50" t="inlineStr"/>
-      <c r="BI50" t="inlineStr"/>
-      <c r="BJ50" t="inlineStr"/>
-      <c r="BK50" t="n">
-        <v>0.05023420865862314</v>
+      <c r="BG50" t="inlineStr">
+        <is>
+          <t>Civilians (Democratic Republic of Congo)</t>
+        </is>
+      </c>
+      <c r="BH50" t="inlineStr">
+        <is>
+          <t>Protestant Christian Group (Democratic Republic of Congo); Teachers (Democratic Republic of Congo)</t>
+        </is>
+      </c>
+      <c r="BI50" t="inlineStr">
+        <is>
+          <t>On 27 April 2024, unidentified armed men abducted the head of Bukavu's ISP (Higher Teaching Institute) and a woman, the spouse of the man, in Luberizi (Ruzizi, Uvira, Sud-Kivu). The director is also a Pentecostal pastor and a former MP. Youth protested to demand their release (coded separately). The abductees were released on 29 April 2024. No further details on their release.</t>
+        </is>
+      </c>
+      <c r="BJ50" t="inlineStr">
+        <is>
+          <t>2024-04-27</t>
+        </is>
+      </c>
+      <c r="BK50" t="inlineStr">
+        <is>
+          <t>Uvira</t>
+        </is>
+      </c>
+      <c r="BL50" t="n">
+        <v>0.1000427476021267</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CD6210ZS01</t>
+          <t>CD6208ZS03</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -6883,205 +7440,112 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CD6210ZS04</t>
+          <t>CD6208ZS03</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD6208ZS03</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>64.90000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="I51" t="n">
-        <v>21.9</v>
+        <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K51" t="n">
-        <v>10.2</v>
+        <v>0.3</v>
       </c>
       <c r="L51" t="n">
-        <v>35.1</v>
+        <v>22.3</v>
       </c>
       <c r="M51" t="n">
-        <v>101.73</v>
+        <v>80.81</v>
       </c>
       <c r="N51" t="n">
-        <v>5.880000000000001</v>
+        <v>6</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>0.78</v>
+        <v>1.37</v>
       </c>
       <c r="S51" t="n">
-        <v>8.879999999999999</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>31.91</v>
+        <v>0.34</v>
       </c>
       <c r="X51" t="n">
         <v>0</v>
       </c>
-      <c r="Y51" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>6</v>
-      </c>
-      <c r="AP51" t="inlineStr">
-        <is>
-          <t>2025-04-21 ---- 2025-03-03 ---- 2025-03-03 ---- 2025-03-03 ---- 2025-03-03 ---- 2024-09-22</t>
-        </is>
-      </c>
-      <c r="AQ51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">April 2025: An education facility was burned during intense fighting between unidentified conflict parties. ---- March 2025: A school was taken over and converted into a military camp.  ---- March 2025: A school was taken over and converted into a military camp.  ---- March 2025: A school was taken over and converted into a military camp.  ---- March 2025: A school was taken over and converted into a military camp.  ---- September 2024: A teacher was shot dead by an unidentified armed group. </t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Unspecified Location</t>
-        </is>
-      </c>
-      <c r="AS51" t="inlineStr">
-        <is>
-          <t>Other ---- No Information ---- No Information ---- No Information ---- No Information ---- NSA</t>
-        </is>
-      </c>
-      <c r="AT51" t="inlineStr">
-        <is>
-          <t>Conflict Party unspecified (DRC) ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor</t>
-        </is>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>Arson ---- Firearms ---- Firearms ---- Firearms ---- Firearms ---- Firearms</t>
-        </is>
-      </c>
-      <c r="AV51" t="inlineStr">
-        <is>
-          <t>School: No Further Details ---- School: No Further Details ---- School: No Further Details ---- School: No Further Details ---- School: No Further Details ---- Not Applicable</t>
-        </is>
-      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr"/>
+      <c r="AJ51" t="inlineStr"/>
+      <c r="AK51" t="inlineStr"/>
+      <c r="AL51" t="inlineStr"/>
+      <c r="AM51" t="inlineStr"/>
+      <c r="AN51" t="inlineStr"/>
+      <c r="AO51" t="inlineStr"/>
+      <c r="AP51" t="inlineStr"/>
+      <c r="AQ51" t="inlineStr"/>
+      <c r="AR51" t="inlineStr"/>
+      <c r="AS51" t="inlineStr"/>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AU51" t="inlineStr"/>
+      <c r="AV51" t="inlineStr"/>
       <c r="AW51" t="inlineStr"/>
       <c r="AX51" t="inlineStr"/>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>Sud-Kivu</t>
-        </is>
-      </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>Fizi</t>
-        </is>
-      </c>
-      <c r="BA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB51" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC51" t="inlineStr">
-        <is>
-          <t>Strategic developments</t>
-        </is>
-      </c>
-      <c r="BD51" t="inlineStr">
-        <is>
-          <t>Headquarters or base established</t>
-        </is>
-      </c>
-      <c r="BE51" t="inlineStr">
-        <is>
-          <t>Military Forces of the Democratic Republic of Congo (2019-)</t>
-        </is>
-      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr"/>
+      <c r="BA51" t="inlineStr"/>
+      <c r="BB51" t="inlineStr"/>
+      <c r="BC51" t="inlineStr"/>
+      <c r="BD51" t="inlineStr"/>
+      <c r="BE51" t="inlineStr"/>
       <c r="BF51" t="inlineStr"/>
       <c r="BG51" t="inlineStr"/>
       <c r="BH51" t="inlineStr"/>
-      <c r="BI51" t="inlineStr">
-        <is>
-          <t>Around 3 March 2025 (as reported), suspected FARDC established their bases in 4 schools in Fizi territory, coded to the territorial town Fizi (Fizi, Sud-Kivu). This occupation impacted at least two thousand children who cannot go to school.</t>
-        </is>
-      </c>
-      <c r="BJ51" t="inlineStr">
-        <is>
-          <t>03 March 2025</t>
-        </is>
-      </c>
-      <c r="BK51" t="n">
-        <v>0.1647060491962532</v>
+      <c r="BI51" t="inlineStr"/>
+      <c r="BJ51" t="inlineStr"/>
+      <c r="BK51" t="inlineStr"/>
+      <c r="BL51" t="n">
+        <v>0.06883975686326899</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CD6210ZS01</t>
+          <t>CD6208ZS04</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -7090,213 +7554,112 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CD6210ZS04</t>
+          <t>CD5407ZS06</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS03;CD5402ZS06;CD5405ZS12;CD5407ZS06;CD6104ZS01;CD6107ZS05;CD6201ZS02;CD6202ZS01;CD6205ZS01;CD6207ZS01;CD6207ZS02;CD6208ZS04;CD6212ZS03</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>64.90000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>21.9</v>
+        <v>20.2</v>
       </c>
       <c r="J52" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="K52" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>35.1</v>
+        <v>20.9</v>
       </c>
       <c r="M52" t="n">
-        <v>101.73</v>
+        <v>66.03999999999999</v>
       </c>
       <c r="N52" t="n">
-        <v>5.880000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>8.879999999999999</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>31.91</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
         <v>0</v>
       </c>
-      <c r="Y52" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO52" t="n">
-        <v>6</v>
-      </c>
-      <c r="AP52" t="inlineStr">
-        <is>
-          <t>2025-04-21 ---- 2025-03-03 ---- 2025-03-03 ---- 2025-03-03 ---- 2025-03-03 ---- 2024-09-22</t>
-        </is>
-      </c>
-      <c r="AQ52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">April 2025: An education facility was burned during intense fighting between unidentified conflict parties. ---- March 2025: A school was taken over and converted into a military camp.  ---- March 2025: A school was taken over and converted into a military camp.  ---- March 2025: A school was taken over and converted into a military camp.  ---- March 2025: A school was taken over and converted into a military camp.  ---- September 2024: A teacher was shot dead by an unidentified armed group. </t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Unspecified Location</t>
-        </is>
-      </c>
-      <c r="AS52" t="inlineStr">
-        <is>
-          <t>Other ---- No Information ---- No Information ---- No Information ---- No Information ---- NSA</t>
-        </is>
-      </c>
-      <c r="AT52" t="inlineStr">
-        <is>
-          <t>Conflict Party unspecified (DRC) ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor</t>
-        </is>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>Arson ---- Firearms ---- Firearms ---- Firearms ---- Firearms ---- Firearms</t>
-        </is>
-      </c>
-      <c r="AV52" t="inlineStr">
-        <is>
-          <t>School: No Further Details ---- School: No Further Details ---- School: No Further Details ---- School: No Further Details ---- School: No Further Details ---- Not Applicable</t>
-        </is>
-      </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr"/>
+      <c r="AJ52" t="inlineStr"/>
+      <c r="AK52" t="inlineStr"/>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="inlineStr"/>
+      <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
+      <c r="AP52" t="inlineStr"/>
+      <c r="AQ52" t="inlineStr"/>
+      <c r="AR52" t="inlineStr"/>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AU52" t="inlineStr"/>
+      <c r="AV52" t="inlineStr"/>
       <c r="AW52" t="inlineStr"/>
       <c r="AX52" t="inlineStr"/>
-      <c r="AY52" t="inlineStr">
-        <is>
-          <t>Sud-Kivu</t>
-        </is>
-      </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>Fizi</t>
-        </is>
-      </c>
-      <c r="BA52" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB52" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC52" t="inlineStr">
-        <is>
-          <t>Violence against civilians</t>
-        </is>
-      </c>
-      <c r="BD52" t="inlineStr">
-        <is>
-          <t>Attack</t>
-        </is>
-      </c>
-      <c r="BE52" t="inlineStr">
-        <is>
-          <t>Unidentified Armed Group (Democratic Republic of Congo)</t>
-        </is>
-      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr"/>
+      <c r="BA52" t="inlineStr"/>
+      <c r="BB52" t="inlineStr"/>
+      <c r="BC52" t="inlineStr"/>
+      <c r="BD52" t="inlineStr"/>
+      <c r="BE52" t="inlineStr"/>
       <c r="BF52" t="inlineStr"/>
-      <c r="BG52" t="inlineStr">
-        <is>
-          <t>Civilians (Democratic Republic of Congo)</t>
-        </is>
-      </c>
-      <c r="BH52" t="inlineStr">
-        <is>
-          <t>Teachers (Democratic Republic of Congo)</t>
-        </is>
-      </c>
-      <c r="BI52" t="inlineStr">
-        <is>
-          <t>On 22 September 2024, an unidentified armed group shot dead a teacher in Baraka (Mutambala, Fizi, Sud-Kivu). No further details.</t>
-        </is>
-      </c>
-      <c r="BJ52" t="inlineStr">
-        <is>
-          <t>22 September 2024</t>
-        </is>
-      </c>
-      <c r="BK52" t="n">
-        <v>0.1647060491962532</v>
+      <c r="BG52" t="inlineStr"/>
+      <c r="BH52" t="inlineStr"/>
+      <c r="BI52" t="inlineStr"/>
+      <c r="BJ52" t="inlineStr"/>
+      <c r="BK52" t="inlineStr"/>
+      <c r="BL52" t="n">
+        <v>0.05023420865862314</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CD6210ZS02</t>
+          <t>CD6210ZS01</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -7305,111 +7668,210 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CD6210ZS01</t>
+          <t>CD6210ZS04</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>79.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>11.2</v>
+        <v>21.9</v>
       </c>
       <c r="J53" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="K53" t="n">
-        <v>6.7</v>
+        <v>10.2</v>
       </c>
       <c r="L53" t="n">
-        <v>20.8</v>
+        <v>35.1</v>
       </c>
       <c r="M53" t="n">
-        <v>73.83</v>
+        <v>101.73</v>
       </c>
       <c r="N53" t="n">
-        <v>1.14</v>
+        <v>5.880000000000001</v>
       </c>
       <c r="O53" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>0.57</v>
+        <v>2.31</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="S53" t="n">
-        <v>3.41</v>
+        <v>8.879999999999999</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="U53" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W53" t="n">
-        <v>20.37</v>
+        <v>31.91</v>
       </c>
       <c r="X53" t="n">
         <v>0</v>
       </c>
-      <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr"/>
-      <c r="AA53" t="inlineStr"/>
-      <c r="AB53" t="inlineStr"/>
-      <c r="AC53" t="inlineStr"/>
-      <c r="AD53" t="inlineStr"/>
-      <c r="AE53" t="inlineStr"/>
-      <c r="AF53" t="inlineStr"/>
-      <c r="AG53" t="inlineStr"/>
-      <c r="AH53" t="inlineStr"/>
-      <c r="AI53" t="inlineStr"/>
-      <c r="AJ53" t="inlineStr"/>
-      <c r="AK53" t="inlineStr"/>
-      <c r="AL53" t="inlineStr"/>
-      <c r="AM53" t="inlineStr"/>
-      <c r="AN53" t="inlineStr"/>
-      <c r="AO53" t="inlineStr"/>
-      <c r="AP53" t="inlineStr"/>
-      <c r="AQ53" t="inlineStr"/>
-      <c r="AR53" t="inlineStr"/>
-      <c r="AS53" t="inlineStr"/>
-      <c r="AT53" t="inlineStr"/>
-      <c r="AU53" t="inlineStr"/>
-      <c r="AV53" t="inlineStr"/>
+      <c r="Y53" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>2025-04-21 ---- 2025-03-03 ---- 2025-03-03 ---- 2025-03-03 ---- 2025-03-03 ---- 2025-03-03 ---- 2024-09-22</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">April 2025: An education facility was burned during intense fighting between unidentified conflict parties. ---- March 2025: A school was taken over and converted into a military camp.  ---- March 2025: A school was taken over and converted into a military camp.  ---- March 2025: A school was taken over and converted into a military camp.  ---- March 2025: A school was taken over and converted into a military camp.  ---- March 2025: An unspecified number of educational facilties were destroyed by Wazalendo. ---- September 2024: A teacher was shot dead by an unidentified armed group. </t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Unspecified Location</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>Other ---- No Information ---- No Information ---- No Information ---- No Information ---- NSA ---- NSA</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr">
+        <is>
+          <t>Conflict Party unspecified (DRC) ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Wazalendo (DRC local militia) ---- Unidentified Armed Actor</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>Arson ---- Firearms ---- Firearms ---- Firearms ---- Firearms ---- Firearms ---- Firearms</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>School: No Further Details ---- School: No Further Details ---- School: No Further Details ---- School: No Further Details ---- School: No Further Details ---- School: No Further Details ---- Not Applicable</t>
+        </is>
+      </c>
       <c r="AW53" t="inlineStr"/>
       <c r="AX53" t="inlineStr"/>
-      <c r="AY53" t="inlineStr"/>
-      <c r="AZ53" t="inlineStr"/>
-      <c r="BA53" t="inlineStr"/>
-      <c r="BB53" t="inlineStr"/>
-      <c r="BC53" t="inlineStr"/>
-      <c r="BD53" t="inlineStr"/>
-      <c r="BE53" t="inlineStr"/>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Sud-Kivu</t>
+        </is>
+      </c>
+      <c r="AZ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>Sud-Kivu</t>
+        </is>
+      </c>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>Strategic developments</t>
+        </is>
+      </c>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>Headquarters or base established</t>
+        </is>
+      </c>
+      <c r="BE53" t="inlineStr">
+        <is>
+          <t>Military Forces of the Democratic Republic of Congo (2019-)</t>
+        </is>
+      </c>
       <c r="BF53" t="inlineStr"/>
       <c r="BG53" t="inlineStr"/>
       <c r="BH53" t="inlineStr"/>
-      <c r="BI53" t="inlineStr"/>
-      <c r="BJ53" t="inlineStr"/>
-      <c r="BK53" t="n">
-        <v>0.3303466278152128</v>
+      <c r="BI53" t="inlineStr">
+        <is>
+          <t>Around 3 March 2025 (as reported), suspected FARDC established their bases in 4 schools in Fizi territory, coded to the territorial town Fizi (Fizi, Sud-Kivu). This occupation impacted at least two thousand children who cannot go to school.</t>
+        </is>
+      </c>
+      <c r="BJ53" t="inlineStr">
+        <is>
+          <t>2025-03-03</t>
+        </is>
+      </c>
+      <c r="BK53" t="inlineStr">
+        <is>
+          <t>Fizi</t>
+        </is>
+      </c>
+      <c r="BL53" t="n">
+        <v>0.1647060491962532</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CD6210ZS04</t>
+          <t>CD6210ZS01</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -7418,89 +7880,151 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CD6210ZS01</t>
+          <t>CD6210ZS04</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>67.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>21.3</v>
+        <v>21.9</v>
       </c>
       <c r="J54" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="K54" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="L54" t="n">
-        <v>32.8</v>
+        <v>35.1</v>
       </c>
       <c r="M54" t="n">
-        <v>64.70999999999999</v>
+        <v>101.73</v>
       </c>
       <c r="N54" t="n">
-        <v>0.63</v>
+        <v>5.880000000000001</v>
       </c>
       <c r="O54" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>8.879999999999999</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W54" t="n">
-        <v>29.82</v>
+        <v>31.91</v>
       </c>
       <c r="X54" t="n">
         <v>0</v>
       </c>
-      <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr"/>
-      <c r="AA54" t="inlineStr"/>
-      <c r="AB54" t="inlineStr"/>
-      <c r="AC54" t="inlineStr"/>
-      <c r="AD54" t="inlineStr"/>
-      <c r="AE54" t="inlineStr"/>
-      <c r="AF54" t="inlineStr"/>
-      <c r="AG54" t="inlineStr"/>
-      <c r="AH54" t="inlineStr"/>
-      <c r="AI54" t="inlineStr"/>
-      <c r="AJ54" t="inlineStr"/>
-      <c r="AK54" t="inlineStr"/>
-      <c r="AL54" t="inlineStr"/>
-      <c r="AM54" t="inlineStr"/>
-      <c r="AN54" t="inlineStr"/>
-      <c r="AO54" t="inlineStr"/>
-      <c r="AP54" t="inlineStr"/>
-      <c r="AQ54" t="inlineStr"/>
-      <c r="AR54" t="inlineStr"/>
-      <c r="AS54" t="inlineStr"/>
-      <c r="AT54" t="inlineStr"/>
-      <c r="AU54" t="inlineStr"/>
-      <c r="AV54" t="inlineStr"/>
+      <c r="Y54" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>2025-04-21 ---- 2025-03-03 ---- 2025-03-03 ---- 2025-03-03 ---- 2025-03-03 ---- 2025-03-03 ---- 2024-09-22</t>
+        </is>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">April 2025: An education facility was burned during intense fighting between unidentified conflict parties. ---- March 2025: A school was taken over and converted into a military camp.  ---- March 2025: A school was taken over and converted into a military camp.  ---- March 2025: A school was taken over and converted into a military camp.  ---- March 2025: A school was taken over and converted into a military camp.  ---- March 2025: An unspecified number of educational facilties were destroyed by Wazalendo. ---- September 2024: A teacher was shot dead by an unidentified armed group. </t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Unspecified Location</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
+          <t>Other ---- No Information ---- No Information ---- No Information ---- No Information ---- NSA ---- NSA</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr">
+        <is>
+          <t>Conflict Party unspecified (DRC) ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Wazalendo (DRC local militia) ---- Unidentified Armed Actor</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>Arson ---- Firearms ---- Firearms ---- Firearms ---- Firearms ---- Firearms ---- Firearms</t>
+        </is>
+      </c>
+      <c r="AV54" t="inlineStr">
+        <is>
+          <t>School: No Further Details ---- School: No Further Details ---- School: No Further Details ---- School: No Further Details ---- School: No Further Details ---- School: No Further Details ---- Not Applicable</t>
+        </is>
+      </c>
       <c r="AW54" t="inlineStr"/>
       <c r="AX54" t="inlineStr"/>
       <c r="AY54" t="inlineStr">
@@ -7508,61 +8032,66 @@
           <t>Sud-Kivu</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
+      <c r="AZ54" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>Sud-Kivu</t>
+        </is>
+      </c>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>Violence against civilians ---- Violence against civilians</t>
+        </is>
+      </c>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>Attack ---- Attack</t>
+        </is>
+      </c>
+      <c r="BE54" t="inlineStr">
+        <is>
+          <t>Unidentified Armed Group (Democratic Republic of Congo) ---- EPLC: Awakening of Patriots for the Liberation of Congo (Wazalendo)</t>
+        </is>
+      </c>
+      <c r="BF54" t="inlineStr"/>
+      <c r="BG54" t="inlineStr">
+        <is>
+          <t>Civilians (Democratic Republic of Congo) ---- Civilians (Democratic Republic of Congo)</t>
+        </is>
+      </c>
+      <c r="BH54" t="inlineStr">
+        <is>
+          <t>Teachers (Democratic Republic of Congo) ---- Health Workers (Democratic Republic of Congo); Banyamulenge Ethnic Group (Democratic Republic of Congo)</t>
+        </is>
+      </c>
+      <c r="BI54" t="inlineStr">
+        <is>
+          <t>On 22 September 2024, an unidentified armed group shot dead a teacher in Baraka (Mutambala, Fizi, Sud-Kivu). No further details. ---- On 3 March 2025, Wazalendo attacked several Banyamulenge villages (unspecified) within a 10 kilometer radius around Bibogobobo (Mutambala, Fizi, Sud-Kivu). They said they came to 'clean out' the Banyamulenge. They killed 7 people and destroyed houses, health centers, and schools.</t>
+        </is>
+      </c>
+      <c r="BJ54" t="inlineStr">
+        <is>
+          <t>2024-09-22 ---- 2025-03-03</t>
+        </is>
+      </c>
+      <c r="BK54" t="inlineStr">
         <is>
           <t>Fizi</t>
         </is>
       </c>
-      <c r="BA54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB54" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC54" t="inlineStr">
-        <is>
-          <t>Riots</t>
-        </is>
-      </c>
-      <c r="BD54" t="inlineStr">
-        <is>
-          <t>Violent demonstration</t>
-        </is>
-      </c>
-      <c r="BE54" t="inlineStr">
-        <is>
-          <t>Rioters (Democratic Republic of Congo)</t>
-        </is>
-      </c>
-      <c r="BF54" t="inlineStr">
-        <is>
-          <t>Students (Democratic Republic of Congo)</t>
-        </is>
-      </c>
-      <c r="BG54" t="inlineStr">
-        <is>
-          <t>Civilians (Democratic Republic of Congo)</t>
-        </is>
-      </c>
-      <c r="BH54" t="inlineStr"/>
-      <c r="BI54" t="inlineStr">
-        <is>
-          <t>On 10 January 2024, students armed with machetes, stones and tree branchs staged a demonstration against the death of a fellow student at Neema Institute in Abondoki, in Mboko (Tanganyika, Fizi, Sud-Kivu). They gathered as the mourning site, alleging that their colleague had been bewitched by her grandfather and who was narrowly escaped harm. They burned a house and vandalized several properties.</t>
-        </is>
-      </c>
-      <c r="BJ54" t="inlineStr">
-        <is>
-          <t>10 January 2024</t>
-        </is>
-      </c>
-      <c r="BK54" t="n">
-        <v>0.1919372640139413</v>
+      <c r="BL54" t="n">
+        <v>0.1647060491962532</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CD6212ZS01</t>
+          <t>CD6210ZS02</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -7571,61 +8100,61 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CD6210ZS02</t>
+          <t>CD6210ZS01</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>27.4</v>
+        <v>79.2</v>
       </c>
       <c r="I55" t="n">
-        <v>10.2</v>
+        <v>11.2</v>
       </c>
       <c r="J55" t="n">
-        <v>18.7</v>
+        <v>2.9</v>
       </c>
       <c r="K55" t="n">
-        <v>43.8</v>
+        <v>6.7</v>
       </c>
       <c r="L55" t="n">
-        <v>72.59999999999999</v>
+        <v>20.8</v>
       </c>
       <c r="M55" t="n">
-        <v>25.98</v>
+        <v>73.83</v>
       </c>
       <c r="N55" t="n">
-        <v>95.73999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="O55" t="n">
-        <v>1.52</v>
+        <v>4.55</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="T55" t="n">
         <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V55" t="n">
         <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>201.45</v>
+        <v>20.37</v>
       </c>
       <c r="X55" t="n">
         <v>0</v>
@@ -7668,14 +8197,15 @@
       <c r="BH55" t="inlineStr"/>
       <c r="BI55" t="inlineStr"/>
       <c r="BJ55" t="inlineStr"/>
-      <c r="BK55" t="n">
-        <v>0.2784023375594295</v>
+      <c r="BK55" t="inlineStr"/>
+      <c r="BL55" t="n">
+        <v>0.3303466278152128</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CD6212ZS02</t>
+          <t>CD6210ZS04</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -7684,40 +8214,40 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CD6207ZS03</t>
+          <t>CD6210ZS01</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>52.2</v>
+        <v>67.2</v>
       </c>
       <c r="I56" t="n">
-        <v>41.6</v>
+        <v>21.3</v>
       </c>
       <c r="J56" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="K56" t="n">
-        <v>0.6</v>
+        <v>10</v>
       </c>
       <c r="L56" t="n">
-        <v>47.8</v>
+        <v>32.8</v>
       </c>
       <c r="M56" t="n">
-        <v>74.25</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="N56" t="n">
-        <v>2.06</v>
+        <v>0.63</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P56" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -7726,10 +8256,10 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>21.82</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
@@ -7738,7 +8268,7 @@
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>0.76</v>
+        <v>29.82</v>
       </c>
       <c r="X56" t="n">
         <v>0</v>
@@ -7769,26 +8299,71 @@
       <c r="AV56" t="inlineStr"/>
       <c r="AW56" t="inlineStr"/>
       <c r="AX56" t="inlineStr"/>
-      <c r="AY56" t="inlineStr"/>
-      <c r="AZ56" t="inlineStr"/>
-      <c r="BA56" t="inlineStr"/>
-      <c r="BB56" t="inlineStr"/>
-      <c r="BC56" t="inlineStr"/>
-      <c r="BD56" t="inlineStr"/>
-      <c r="BE56" t="inlineStr"/>
-      <c r="BF56" t="inlineStr"/>
-      <c r="BG56" t="inlineStr"/>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Sud-Kivu</t>
+        </is>
+      </c>
+      <c r="AZ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB56" t="inlineStr">
+        <is>
+          <t>Sud-Kivu</t>
+        </is>
+      </c>
+      <c r="BC56" t="inlineStr">
+        <is>
+          <t>Riots</t>
+        </is>
+      </c>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>Violent demonstration</t>
+        </is>
+      </c>
+      <c r="BE56" t="inlineStr">
+        <is>
+          <t>Rioters (Democratic Republic of Congo)</t>
+        </is>
+      </c>
+      <c r="BF56" t="inlineStr">
+        <is>
+          <t>Students (Democratic Republic of Congo)</t>
+        </is>
+      </c>
+      <c r="BG56" t="inlineStr">
+        <is>
+          <t>Civilians (Democratic Republic of Congo)</t>
+        </is>
+      </c>
       <c r="BH56" t="inlineStr"/>
-      <c r="BI56" t="inlineStr"/>
-      <c r="BJ56" t="inlineStr"/>
-      <c r="BK56" t="n">
-        <v>0.1621506495965166</v>
+      <c r="BI56" t="inlineStr">
+        <is>
+          <t>On 10 January 2024, students armed with machetes, stones and tree branchs staged a demonstration against the death of a fellow student at Neema Institute in Abondoki, in Mboko (Tanganyika, Fizi, Sud-Kivu). They gathered as the mourning site, alleging that their colleague had been bewitched by her grandfather and who was narrowly escaped harm. They burned a house and vandalized several properties.</t>
+        </is>
+      </c>
+      <c r="BJ56" t="inlineStr">
+        <is>
+          <t>2024-01-10</t>
+        </is>
+      </c>
+      <c r="BK56" t="inlineStr">
+        <is>
+          <t>Fizi</t>
+        </is>
+      </c>
+      <c r="BL56" t="n">
+        <v>0.1919372640139413</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CD6212ZS03</t>
+          <t>CD6212ZS01</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -7797,40 +8372,40 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CD6207ZS01</t>
+          <t>CD6210ZS02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>CD5402ZS03;CD5402ZS06;CD5405ZS09;CD5405ZS12;CD5407ZS06;CD6104ZS01;CD6107ZS05;CD6201ZS02;CD6202ZS01;CD6205ZS01;CD6207ZS01;CD6207ZS02;CD6208ZS04;CD6212ZS03</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>51.9</v>
+        <v>27.4</v>
       </c>
       <c r="I57" t="n">
-        <v>40</v>
+        <v>10.2</v>
       </c>
       <c r="J57" t="n">
-        <v>8.1</v>
+        <v>18.7</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>43.8</v>
       </c>
       <c r="L57" t="n">
-        <v>48.1</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="M57" t="n">
-        <v>60.63</v>
+        <v>25.98</v>
       </c>
       <c r="N57" t="n">
-        <v>8.69</v>
+        <v>95.73999999999999</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="P57" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -7842,7 +8417,7 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>21.95</v>
+        <v>0</v>
       </c>
       <c r="U57" t="n">
         <v>0</v>
@@ -7851,7 +8426,7 @@
         <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>201.45</v>
       </c>
       <c r="X57" t="n">
         <v>0</v>
@@ -7894,14 +8469,15 @@
       <c r="BH57" t="inlineStr"/>
       <c r="BI57" t="inlineStr"/>
       <c r="BJ57" t="inlineStr"/>
-      <c r="BK57" t="n">
-        <v>0.2842257999783894</v>
+      <c r="BK57" t="inlineStr"/>
+      <c r="BL57" t="n">
+        <v>0.2784023375594295</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CD6212ZS04</t>
+          <t>CD6212ZS02</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -7910,52 +8486,52 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CD6202ZS03</t>
+          <t>CD6207ZS03</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>76</v>
+        <v>52.2</v>
       </c>
       <c r="I58" t="n">
-        <v>22.2</v>
+        <v>41.6</v>
       </c>
       <c r="J58" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="K58" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="L58" t="n">
-        <v>24</v>
+        <v>47.8</v>
       </c>
       <c r="M58" t="n">
-        <v>57.42</v>
+        <v>74.25</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>0.47</v>
+        <v>1.03</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>5.35</v>
+        <v>4.88</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>21.82</v>
       </c>
       <c r="U58" t="n">
         <v>0</v>
@@ -7964,7 +8540,7 @@
         <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>2.44</v>
+        <v>0.76</v>
       </c>
       <c r="X58" t="n">
         <v>0</v>
@@ -8007,14 +8583,15 @@
       <c r="BH58" t="inlineStr"/>
       <c r="BI58" t="inlineStr"/>
       <c r="BJ58" t="inlineStr"/>
-      <c r="BK58" t="n">
-        <v>0.092529048039682</v>
+      <c r="BK58" t="inlineStr"/>
+      <c r="BL58" t="n">
+        <v>0.1621506495965166</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CD6212ZS05</t>
+          <t>CD6212ZS03</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -8023,52 +8600,52 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CD5407ZS02</t>
+          <t>CD6207ZS01</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS03;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6208ZS03;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+          <t>CD5402ZS03;CD5402ZS06;CD5405ZS12;CD5407ZS06;CD6104ZS01;CD6107ZS05;CD6201ZS02;CD6202ZS01;CD6205ZS01;CD6207ZS01;CD6207ZS02;CD6208ZS04;CD6212ZS03</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>60.7</v>
+        <v>51.9</v>
       </c>
       <c r="I59" t="n">
-        <v>32.7</v>
+        <v>40</v>
       </c>
       <c r="J59" t="n">
-        <v>6.4</v>
+        <v>8.1</v>
       </c>
       <c r="K59" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>39.3</v>
+        <v>48.1</v>
       </c>
       <c r="M59" t="n">
-        <v>96.63</v>
+        <v>60.63</v>
       </c>
       <c r="N59" t="n">
-        <v>1.05</v>
+        <v>8.69</v>
       </c>
       <c r="O59" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>3.75</v>
+        <v>1.39</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>9.32</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>2.7</v>
+        <v>21.95</v>
       </c>
       <c r="U59" t="n">
         <v>0</v>
@@ -8077,7 +8654,7 @@
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>5.13</v>
+        <v>0</v>
       </c>
       <c r="X59" t="n">
         <v>0</v>
@@ -8120,7 +8697,236 @@
       <c r="BH59" t="inlineStr"/>
       <c r="BI59" t="inlineStr"/>
       <c r="BJ59" t="inlineStr"/>
-      <c r="BK59" t="n">
+      <c r="BK59" t="inlineStr"/>
+      <c r="BL59" t="n">
+        <v>0.2842257999783894</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>CD6212ZS04</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>CD6202ZS03</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>76</v>
+      </c>
+      <c r="I60" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L60" t="n">
+        <v>24</v>
+      </c>
+      <c r="M60" t="n">
+        <v>57.42</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="X60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr"/>
+      <c r="AC60" t="inlineStr"/>
+      <c r="AD60" t="inlineStr"/>
+      <c r="AE60" t="inlineStr"/>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="inlineStr"/>
+      <c r="AH60" t="inlineStr"/>
+      <c r="AI60" t="inlineStr"/>
+      <c r="AJ60" t="inlineStr"/>
+      <c r="AK60" t="inlineStr"/>
+      <c r="AL60" t="inlineStr"/>
+      <c r="AM60" t="inlineStr"/>
+      <c r="AN60" t="inlineStr"/>
+      <c r="AO60" t="inlineStr"/>
+      <c r="AP60" t="inlineStr"/>
+      <c r="AQ60" t="inlineStr"/>
+      <c r="AR60" t="inlineStr"/>
+      <c r="AS60" t="inlineStr"/>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AU60" t="inlineStr"/>
+      <c r="AV60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr"/>
+      <c r="AX60" t="inlineStr"/>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr"/>
+      <c r="BA60" t="inlineStr"/>
+      <c r="BB60" t="inlineStr"/>
+      <c r="BC60" t="inlineStr"/>
+      <c r="BD60" t="inlineStr"/>
+      <c r="BE60" t="inlineStr"/>
+      <c r="BF60" t="inlineStr"/>
+      <c r="BG60" t="inlineStr"/>
+      <c r="BH60" t="inlineStr"/>
+      <c r="BI60" t="inlineStr"/>
+      <c r="BJ60" t="inlineStr"/>
+      <c r="BK60" t="inlineStr"/>
+      <c r="BL60" t="n">
+        <v>0.092529048039682</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>CD6212ZS05</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>CD5407ZS02</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>CD5402ZS02;CD5402ZS04;CD5403ZS02;CD5403ZS03;CD5403ZS04;CD5405ZS03;CD5405ZS04;CD5405ZS05;CD5405ZS07;CD5405ZS08;CD5405ZS11;CD5405ZS13;CD5407ZS01;CD5407ZS02;CD5407ZS04;CD5407ZS05;CD5409ZS04;CD6101ZS01;CD6101ZS02;CD6104ZS04;CD6107ZS02;CD6107ZS06;CD6201ZS01;CD6202ZS03;CD6202ZS04;CD6202ZS05;CD6205ZS02;CD6205ZS03;CD6205ZS04;CD6207ZS03;CD6208ZS02;CD6210ZS01;CD6210ZS02;CD6210ZS04;CD6212ZS01;CD6212ZS02;CD6212ZS04;CD6212ZS05</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="I61" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="J61" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L61" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="M61" t="n">
+        <v>96.63</v>
+      </c>
+      <c r="N61" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="O61" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="P61" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="X61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="inlineStr"/>
+      <c r="AD61" t="inlineStr"/>
+      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
+      <c r="AH61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
+      <c r="AL61" t="inlineStr"/>
+      <c r="AM61" t="inlineStr"/>
+      <c r="AN61" t="inlineStr"/>
+      <c r="AO61" t="inlineStr"/>
+      <c r="AP61" t="inlineStr"/>
+      <c r="AQ61" t="inlineStr"/>
+      <c r="AR61" t="inlineStr"/>
+      <c r="AS61" t="inlineStr"/>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AU61" t="inlineStr"/>
+      <c r="AV61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr"/>
+      <c r="AX61" t="inlineStr"/>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr"/>
+      <c r="BA61" t="inlineStr"/>
+      <c r="BB61" t="inlineStr"/>
+      <c r="BC61" t="inlineStr"/>
+      <c r="BD61" t="inlineStr"/>
+      <c r="BE61" t="inlineStr"/>
+      <c r="BF61" t="inlineStr"/>
+      <c r="BG61" t="inlineStr"/>
+      <c r="BH61" t="inlineStr"/>
+      <c r="BI61" t="inlineStr"/>
+      <c r="BJ61" t="inlineStr"/>
+      <c r="BK61" t="inlineStr"/>
+      <c r="BL61" t="n">
         <v>0.107791466648763</v>
       </c>
     </row>
@@ -8130,10 +8936,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C9824523CAB29F4DA646F20BAFE41B4C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9c972c102b01d47663811fb2ebdbd1e4">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5940141-1bc9-4c17-b1bc-e50f6b2083d6" xmlns:ns3="14cbb838-50ff-4dab-9c3f-cddf75f03c13" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bd0e8b72e466adcc572d3af37c1ebe05" ns2:_="" ns3:_="">
-    <xsd:import namespace="b5940141-1bc9-4c17-b1bc-e50f6b2083d6"/>
-    <xsd:import namespace="14cbb838-50ff-4dab-9c3f-cddf75f03c13"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DE51FB2AFBB2DD429D3D11FE759FFC43" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1354c8e90e28409d311bbba5db8dc335">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4877444-78fa-4cfa-bafc-d6c64fafc061" xmlns:ns3="d0fa6634-326e-4532-91a2-52bea7ac9212" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dbb4473bd7833dc3543803a005841490" ns2:_="" ns3:_="">
+    <xsd:import namespace="f4877444-78fa-4cfa-bafc-d6c64fafc061"/>
+    <xsd:import namespace="d0fa6634-326e-4532-91a2-52bea7ac9212"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -8145,13 +8951,15 @@
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
@@ -8160,7 +8968,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b5940141-1bc9-4c17-b1bc-e50f6b2083d6" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f4877444-78fa-4cfa-bafc-d6c64fafc061" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -8178,52 +8986,57 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="14" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="MediaServiceDateTaken" ma:index="13" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="18" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
         </xsd:sequence>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+    <xsd:element name="MediaServiceOCR" ma:index="20" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+    <xsd:element name="MediaServiceSearchProperties" ma:index="21" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="18" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="19" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="21" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="23" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="14cbb838-50ff-4dab-9c3f-cddf75f03c13" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d0fa6634-326e-4532-91a2-52bea7ac9212" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="SharedWithUsers" ma:index="11" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
@@ -8251,6 +9064,17 @@
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="19" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{d6bd4e25-e667-4943-8e38-5db701f530ee}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="d0fa6634-326e-4532-91a2-52bea7ac9212">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -8364,7 +9188,8 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5940141-1bc9-4c17-b1bc-e50f6b2083d6">
+    <TaxCatchAll xmlns="d0fa6634-326e-4532-91a2-52bea7ac9212" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4877444-78fa-4cfa-bafc-d6c64fafc061">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
@@ -8372,13 +9197,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33717AA5-D484-4920-BB19-79D654FBE5E4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF5E8234-EC66-4F82-B663-EC6317B3EFC4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6FA7C15-9A79-44E3-9F52-FC1D154FD9E1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D37518E0-A57A-40FF-9292-D7F381E81FDC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94FC86F4-2D88-4C8D-9169-ECA9E154C659}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBBFA09A-DEA4-4838-95B7-A2F64AA5BFB4}"/>
 </file>